--- a/2026.01.07_Приоритизация_RICE_MoSCoW.xlsx
+++ b/2026.01.07_Приоритизация_RICE_MoSCoW.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\79147\Documents\Документы, инвестиции, личные финансы\2024.07.03_Альфа-банк\Магистратура ВШЭ\20_Магистерская диссертация\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3761FF03-AC84-4A9F-9296-2EF94853FAF4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D023484B-EA15-4DC3-A981-35A7F0853502}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="839" firstSheet="4" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="839" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RICE_четкая модель" sheetId="1" r:id="rId1"/>
@@ -848,12 +848,20 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="12" x14ac:knownFonts="1">
+  <fonts count="13" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -1603,89 +1611,89 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="194">
+  <cellXfs count="191">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="5" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="5" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="5" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="6" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="6" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="6" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1"/>
@@ -1700,31 +1708,31 @@
     <xf numFmtId="3" fontId="0" fillId="5" borderId="25" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="5" borderId="26" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="5" fillId="6" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="5" fillId="6" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="2" fontId="5" fillId="7" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="4" fontId="5" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="4" fontId="5" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="4" fontId="5" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="5" fillId="6" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="5" fillId="7" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="5" fillId="8" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="6" fillId="6" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="6" fillId="6" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="2" fontId="6" fillId="7" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="4" fontId="6" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="4" fontId="6" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="4" fontId="6" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="6" fillId="6" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="6" fillId="7" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="6" fillId="8" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -1748,127 +1756,58 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="4" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="4" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="5" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="4" fontId="6" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="4" fontId="5" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
@@ -1878,32 +1817,17 @@
     <xf numFmtId="4" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1916,14 +1840,95 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="38" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="39" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="45" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="46" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="35" xfId="0" applyBorder="1"/>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="40" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="42" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="43" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="44" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -1933,33 +1938,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="45" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="46" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="35" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="38" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1969,23 +1947,48 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="40" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="1" fillId="0" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="1" fillId="0" borderId="40" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="1" fillId="0" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="1" fillId="0" borderId="42" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="1" fillId="0" borderId="43" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="1" fillId="0" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="1" fillId="0" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="1" fillId="0" borderId="44" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="38" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="39" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="40" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="4" fontId="6" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Гиперссылка" xfId="1" builtinId="8"/>
@@ -2302,21 +2305,21 @@
       </c>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B4" s="106" t="s">
+      <c r="B4" s="152" t="s">
         <v>6</v>
       </c>
-      <c r="C4" s="105" t="s">
+      <c r="C4" s="151" t="s">
         <v>7</v>
       </c>
-      <c r="D4" s="105"/>
-      <c r="E4" s="105"/>
-      <c r="F4" s="105"/>
-      <c r="G4" s="105" t="s">
+      <c r="D4" s="151"/>
+      <c r="E4" s="151"/>
+      <c r="F4" s="151"/>
+      <c r="G4" s="151" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B5" s="107"/>
+      <c r="B5" s="153"/>
       <c r="C5" s="4" t="s">
         <v>1</v>
       </c>
@@ -2329,10 +2332,10 @@
       <c r="F5" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="G5" s="105"/>
+      <c r="G5" s="151"/>
     </row>
     <row r="6" spans="2:7" ht="45" x14ac:dyDescent="0.25">
-      <c r="B6" s="108"/>
+      <c r="B6" s="154"/>
       <c r="C6" s="4" t="s">
         <v>11</v>
       </c>
@@ -2345,7 +2348,7 @@
       <c r="F6" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="G6" s="105"/>
+      <c r="G6" s="151"/>
     </row>
     <row r="7" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B7" s="6">
@@ -2450,17 +2453,17 @@
       </c>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B14" s="112" t="s">
+      <c r="B14" s="158" t="s">
         <v>7</v>
       </c>
-      <c r="C14" s="109" t="s">
+      <c r="C14" s="155" t="s">
         <v>6</v>
       </c>
-      <c r="D14" s="110"/>
-      <c r="E14" s="111"/>
+      <c r="D14" s="156"/>
+      <c r="E14" s="157"/>
     </row>
     <row r="15" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B15" s="113"/>
+      <c r="B15" s="159"/>
       <c r="C15" s="30" t="s">
         <v>8</v>
       </c>
@@ -2608,17 +2611,17 @@
     </row>
     <row r="4" spans="2:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="5" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B5" s="112" t="s">
+      <c r="B5" s="158" t="s">
         <v>7</v>
       </c>
-      <c r="C5" s="109" t="s">
+      <c r="C5" s="155" t="s">
         <v>6</v>
       </c>
-      <c r="D5" s="110"/>
-      <c r="E5" s="111"/>
+      <c r="D5" s="156"/>
+      <c r="E5" s="157"/>
     </row>
     <row r="6" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B6" s="113"/>
+      <c r="B6" s="159"/>
       <c r="C6" s="30" t="s">
         <v>8</v>
       </c>
@@ -2749,18 +2752,18 @@
       <c r="B15" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="C15" s="114" t="s">
+      <c r="C15" s="160" t="s">
         <v>17</v>
       </c>
-      <c r="D15" s="115"/>
-      <c r="E15" s="115"/>
-      <c r="F15" s="116"/>
-      <c r="G15" s="114" t="s">
+      <c r="D15" s="161"/>
+      <c r="E15" s="161"/>
+      <c r="F15" s="162"/>
+      <c r="G15" s="160" t="s">
         <v>18</v>
       </c>
-      <c r="H15" s="115"/>
-      <c r="I15" s="115"/>
-      <c r="J15" s="116"/>
+      <c r="H15" s="161"/>
+      <c r="I15" s="161"/>
+      <c r="J15" s="162"/>
     </row>
     <row r="16" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B16" s="15" t="s">
@@ -3192,18 +3195,18 @@
       <c r="B33" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="C33" s="114" t="s">
+      <c r="C33" s="160" t="s">
         <v>17</v>
       </c>
-      <c r="D33" s="115"/>
-      <c r="E33" s="115"/>
-      <c r="F33" s="116"/>
-      <c r="G33" s="114" t="s">
+      <c r="D33" s="161"/>
+      <c r="E33" s="161"/>
+      <c r="F33" s="162"/>
+      <c r="G33" s="160" t="s">
         <v>18</v>
       </c>
-      <c r="H33" s="115"/>
-      <c r="I33" s="115"/>
-      <c r="J33" s="116"/>
+      <c r="H33" s="161"/>
+      <c r="I33" s="161"/>
+      <c r="J33" s="162"/>
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B34" s="15" t="s">
@@ -3613,18 +3616,18 @@
       <c r="B51" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="C51" s="114" t="s">
+      <c r="C51" s="160" t="s">
         <v>17</v>
       </c>
-      <c r="D51" s="115"/>
-      <c r="E51" s="115"/>
-      <c r="F51" s="116"/>
-      <c r="G51" s="114" t="s">
+      <c r="D51" s="161"/>
+      <c r="E51" s="161"/>
+      <c r="F51" s="162"/>
+      <c r="G51" s="160" t="s">
         <v>18</v>
       </c>
-      <c r="H51" s="115"/>
-      <c r="I51" s="115"/>
-      <c r="J51" s="116"/>
+      <c r="H51" s="161"/>
+      <c r="I51" s="161"/>
+      <c r="J51" s="162"/>
     </row>
     <row r="52" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B52" s="15" t="s">
@@ -4048,13 +4051,13 @@
       <c r="C2" s="98"/>
     </row>
     <row r="3" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="117" t="s">
+      <c r="A3" s="164" t="s">
         <v>98</v>
       </c>
-      <c r="B3" s="118"/>
-      <c r="C3" s="118"/>
-      <c r="D3" s="123"/>
-      <c r="E3" s="123"/>
+      <c r="B3" s="165"/>
+      <c r="C3" s="165"/>
+      <c r="D3" s="166"/>
+      <c r="E3" s="166"/>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
@@ -4071,52 +4074,52 @@
       <c r="C5" s="99"/>
     </row>
     <row r="6" spans="1:10" ht="75.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="129" t="s">
+      <c r="A6" s="163" t="s">
         <v>85</v>
       </c>
-      <c r="B6" s="129" t="s">
+      <c r="B6" s="163" t="s">
         <v>86</v>
       </c>
-      <c r="C6" s="129" t="s">
+      <c r="C6" s="163" t="s">
         <v>87</v>
       </c>
-      <c r="D6" s="129" t="s">
+      <c r="D6" s="163" t="s">
         <v>128</v>
       </c>
-      <c r="E6" s="129"/>
-      <c r="F6" s="129"/>
-      <c r="G6" s="129" t="s">
+      <c r="E6" s="163"/>
+      <c r="F6" s="163"/>
+      <c r="G6" s="163" t="s">
         <v>129</v>
       </c>
-      <c r="H6" s="129"/>
-      <c r="I6" s="129"/>
-      <c r="J6" s="129" t="s">
+      <c r="H6" s="163"/>
+      <c r="I6" s="163"/>
+      <c r="J6" s="163" t="s">
         <v>118</v>
       </c>
     </row>
     <row r="7" spans="1:10" s="97" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="129"/>
-      <c r="B7" s="129"/>
-      <c r="C7" s="129"/>
-      <c r="D7" s="125" t="s">
+      <c r="A7" s="163"/>
+      <c r="B7" s="163"/>
+      <c r="C7" s="163"/>
+      <c r="D7" s="107" t="s">
         <v>114</v>
       </c>
-      <c r="E7" s="125" t="s">
+      <c r="E7" s="107" t="s">
         <v>115</v>
       </c>
-      <c r="F7" s="125" t="s">
+      <c r="F7" s="107" t="s">
         <v>116</v>
       </c>
-      <c r="G7" s="125" t="s">
+      <c r="G7" s="107" t="s">
         <v>114</v>
       </c>
-      <c r="H7" s="125" t="s">
+      <c r="H7" s="107" t="s">
         <v>115</v>
       </c>
-      <c r="I7" s="125" t="s">
+      <c r="I7" s="107" t="s">
         <v>116</v>
       </c>
-      <c r="J7" s="129"/>
+      <c r="J7" s="163"/>
     </row>
     <row r="8" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A8" s="102" t="s">
@@ -4128,24 +4131,24 @@
       <c r="C8" s="103" t="s">
         <v>72</v>
       </c>
-      <c r="D8" s="128" t="s">
+      <c r="D8" s="110" t="s">
         <v>104</v>
       </c>
-      <c r="E8" s="128" t="s">
+      <c r="E8" s="110" t="s">
         <v>105</v>
       </c>
-      <c r="F8" s="128" t="s">
+      <c r="F8" s="110" t="s">
         <v>104</v>
       </c>
-      <c r="G8" s="128">
+      <c r="G8" s="110">
         <f>IF(D8=$A$21,$B$21,(IF(D8=$A$22,$B$22,IF(D8=$A$23,$B$23,$B$24))))</f>
         <v>1</v>
       </c>
-      <c r="H8" s="128">
+      <c r="H8" s="110">
         <f t="shared" ref="H8:I8" si="0">IF(E8=$A$21,$B$21,(IF(E8=$A$22,$B$22,IF(E8=$A$23,$B$23,$B$24))))</f>
         <v>0.66</v>
       </c>
-      <c r="I8" s="128">
+      <c r="I8" s="110">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
@@ -4164,24 +4167,24 @@
       <c r="C9" s="103" t="s">
         <v>88</v>
       </c>
-      <c r="D9" s="128" t="s">
+      <c r="D9" s="110" t="s">
         <v>106</v>
       </c>
-      <c r="E9" s="128" t="s">
+      <c r="E9" s="110" t="s">
         <v>106</v>
       </c>
-      <c r="F9" s="128" t="s">
+      <c r="F9" s="110" t="s">
         <v>105</v>
       </c>
-      <c r="G9" s="128">
+      <c r="G9" s="110">
         <f>IF(D9=$A$21,$B$21,(IF(D9=$A$22,$B$22,IF(D9=$A$23,$B$23,$B$24))))</f>
         <v>0.33</v>
       </c>
-      <c r="H9" s="128">
+      <c r="H9" s="110">
         <f t="shared" ref="H9:H10" si="1">IF(E9=$A$21,$B$21,(IF(E9=$A$22,$B$22,IF(E9=$A$23,$B$23,$B$24))))</f>
         <v>0.33</v>
       </c>
-      <c r="I9" s="128">
+      <c r="I9" s="110">
         <f t="shared" ref="I9:I10" si="2">IF(F9=$A$21,$B$21,(IF(F9=$A$22,$B$22,IF(F9=$A$23,$B$23,$B$24))))</f>
         <v>0.66</v>
       </c>
@@ -4200,24 +4203,24 @@
       <c r="C10" s="103" t="s">
         <v>89</v>
       </c>
-      <c r="D10" s="128" t="s">
+      <c r="D10" s="110" t="s">
         <v>105</v>
       </c>
-      <c r="E10" s="128" t="s">
+      <c r="E10" s="110" t="s">
         <v>105</v>
       </c>
-      <c r="F10" s="128" t="s">
+      <c r="F10" s="110" t="s">
         <v>105</v>
       </c>
-      <c r="G10" s="128">
+      <c r="G10" s="110">
         <f t="shared" ref="G10:G17" si="4">IF(D10=$A$21,$B$21,(IF(D10=$A$22,$B$22,IF(D10=$A$23,$B$23,$B$24))))</f>
         <v>0.66</v>
       </c>
-      <c r="H10" s="128">
+      <c r="H10" s="110">
         <f t="shared" si="1"/>
         <v>0.66</v>
       </c>
-      <c r="I10" s="128">
+      <c r="I10" s="110">
         <f t="shared" si="2"/>
         <v>0.66</v>
       </c>
@@ -4236,24 +4239,24 @@
       <c r="C11" s="103" t="s">
         <v>76</v>
       </c>
-      <c r="D11" s="128" t="s">
+      <c r="D11" s="110" t="s">
         <v>104</v>
       </c>
-      <c r="E11" s="128" t="s">
+      <c r="E11" s="110" t="s">
         <v>105</v>
       </c>
-      <c r="F11" s="128" t="s">
+      <c r="F11" s="110" t="s">
         <v>105</v>
       </c>
-      <c r="G11" s="128">
+      <c r="G11" s="110">
         <f t="shared" si="4"/>
         <v>1</v>
       </c>
-      <c r="H11" s="128">
+      <c r="H11" s="110">
         <f t="shared" ref="H11:H17" si="5">IF(E11=$A$21,$B$21,(IF(E11=$A$22,$B$22,IF(E11=$A$23,$B$23,$B$24))))</f>
         <v>0.66</v>
       </c>
-      <c r="I11" s="128">
+      <c r="I11" s="110">
         <f t="shared" ref="I11:I17" si="6">IF(F11=$A$21,$B$21,(IF(F11=$A$22,$B$22,IF(F11=$A$23,$B$23,$B$24))))</f>
         <v>0.66</v>
       </c>
@@ -4272,24 +4275,24 @@
       <c r="C12" s="103" t="s">
         <v>90</v>
       </c>
-      <c r="D12" s="128" t="s">
+      <c r="D12" s="110" t="s">
         <v>105</v>
       </c>
-      <c r="E12" s="128" t="s">
+      <c r="E12" s="110" t="s">
         <v>104</v>
       </c>
-      <c r="F12" s="128" t="s">
+      <c r="F12" s="110" t="s">
         <v>105</v>
       </c>
-      <c r="G12" s="128">
+      <c r="G12" s="110">
         <f t="shared" si="4"/>
         <v>0.66</v>
       </c>
-      <c r="H12" s="128">
+      <c r="H12" s="110">
         <f t="shared" si="5"/>
         <v>1</v>
       </c>
-      <c r="I12" s="128">
+      <c r="I12" s="110">
         <f t="shared" si="6"/>
         <v>0.66</v>
       </c>
@@ -4308,24 +4311,24 @@
       <c r="C13" s="103" t="s">
         <v>91</v>
       </c>
-      <c r="D13" s="128" t="s">
+      <c r="D13" s="110" t="s">
         <v>104</v>
       </c>
-      <c r="E13" s="128" t="s">
+      <c r="E13" s="110" t="s">
         <v>105</v>
       </c>
-      <c r="F13" s="128" t="s">
+      <c r="F13" s="110" t="s">
         <v>106</v>
       </c>
-      <c r="G13" s="128">
+      <c r="G13" s="110">
         <f t="shared" si="4"/>
         <v>1</v>
       </c>
-      <c r="H13" s="128">
+      <c r="H13" s="110">
         <f t="shared" si="5"/>
         <v>0.66</v>
       </c>
-      <c r="I13" s="128">
+      <c r="I13" s="110">
         <f t="shared" si="6"/>
         <v>0.33</v>
       </c>
@@ -4344,24 +4347,24 @@
       <c r="C14" s="103" t="s">
         <v>92</v>
       </c>
-      <c r="D14" s="128" t="s">
+      <c r="D14" s="110" t="s">
         <v>104</v>
       </c>
-      <c r="E14" s="128" t="s">
+      <c r="E14" s="110" t="s">
         <v>105</v>
       </c>
-      <c r="F14" s="128" t="s">
+      <c r="F14" s="110" t="s">
         <v>106</v>
       </c>
-      <c r="G14" s="128">
+      <c r="G14" s="110">
         <f t="shared" si="4"/>
         <v>1</v>
       </c>
-      <c r="H14" s="128">
+      <c r="H14" s="110">
         <f t="shared" si="5"/>
         <v>0.66</v>
       </c>
-      <c r="I14" s="128">
+      <c r="I14" s="110">
         <f t="shared" si="6"/>
         <v>0.33</v>
       </c>
@@ -4380,24 +4383,24 @@
       <c r="C15" s="103" t="s">
         <v>81</v>
       </c>
-      <c r="D15" s="128" t="s">
+      <c r="D15" s="110" t="s">
         <v>105</v>
       </c>
-      <c r="E15" s="128" t="s">
+      <c r="E15" s="110" t="s">
         <v>104</v>
       </c>
-      <c r="F15" s="128" t="s">
+      <c r="F15" s="110" t="s">
         <v>104</v>
       </c>
-      <c r="G15" s="128">
+      <c r="G15" s="110">
         <f t="shared" si="4"/>
         <v>0.66</v>
       </c>
-      <c r="H15" s="128">
+      <c r="H15" s="110">
         <f t="shared" si="5"/>
         <v>1</v>
       </c>
-      <c r="I15" s="128">
+      <c r="I15" s="110">
         <f t="shared" si="6"/>
         <v>1</v>
       </c>
@@ -4416,24 +4419,24 @@
       <c r="C16" s="103" t="s">
         <v>93</v>
       </c>
-      <c r="D16" s="128" t="s">
+      <c r="D16" s="110" t="s">
         <v>105</v>
       </c>
-      <c r="E16" s="128" t="s">
+      <c r="E16" s="110" t="s">
         <v>104</v>
       </c>
-      <c r="F16" s="128" t="s">
+      <c r="F16" s="110" t="s">
         <v>105</v>
       </c>
-      <c r="G16" s="128">
+      <c r="G16" s="110">
         <f t="shared" si="4"/>
         <v>0.66</v>
       </c>
-      <c r="H16" s="128">
+      <c r="H16" s="110">
         <f t="shared" si="5"/>
         <v>1</v>
       </c>
-      <c r="I16" s="128">
+      <c r="I16" s="110">
         <f t="shared" si="6"/>
         <v>0.66</v>
       </c>
@@ -4452,24 +4455,24 @@
       <c r="C17" s="103" t="s">
         <v>94</v>
       </c>
-      <c r="D17" s="128" t="s">
+      <c r="D17" s="110" t="s">
         <v>106</v>
       </c>
-      <c r="E17" s="128" t="s">
+      <c r="E17" s="110" t="s">
         <v>104</v>
       </c>
-      <c r="F17" s="128" t="s">
+      <c r="F17" s="110" t="s">
         <v>105</v>
       </c>
-      <c r="G17" s="128">
+      <c r="G17" s="110">
         <f t="shared" si="4"/>
         <v>0.33</v>
       </c>
-      <c r="H17" s="128">
+      <c r="H17" s="110">
         <f t="shared" si="5"/>
         <v>1</v>
       </c>
-      <c r="I17" s="128">
+      <c r="I17" s="110">
         <f t="shared" si="6"/>
         <v>0.66</v>
       </c>
@@ -4484,13 +4487,13 @@
       </c>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A20" s="125" t="s">
+      <c r="A20" s="107" t="s">
         <v>103</v>
       </c>
-      <c r="B20" s="126" t="s">
+      <c r="B20" s="108" t="s">
         <v>123</v>
       </c>
-      <c r="C20" s="126" t="s">
+      <c r="C20" s="108" t="s">
         <v>124</v>
       </c>
     </row>
@@ -4544,21 +4547,21 @@
       </c>
     </row>
     <row r="27" spans="1:10" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="125" t="s">
+      <c r="A27" s="107" t="s">
         <v>117</v>
       </c>
-      <c r="B27" s="126" t="s">
+      <c r="B27" s="108" t="s">
         <v>99</v>
       </c>
-      <c r="C27" s="125" t="s">
+      <c r="C27" s="107" t="s">
         <v>108</v>
       </c>
-      <c r="D27" s="127" t="s">
+      <c r="D27" s="109" t="s">
         <v>113</v>
       </c>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A28" s="167" t="s">
+      <c r="A28" s="130" t="s">
         <v>114</v>
       </c>
       <c r="B28" s="104" t="s">
@@ -4567,12 +4570,12 @@
       <c r="C28" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="D28" s="122">
+      <c r="D28" s="105">
         <v>7.5</v>
       </c>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A29" s="168" t="s">
+      <c r="A29" s="131" t="s">
         <v>115</v>
       </c>
       <c r="B29" s="104" t="s">
@@ -4581,12 +4584,12 @@
       <c r="C29" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="D29" s="122">
+      <c r="D29" s="105">
         <v>2.5</v>
       </c>
     </row>
     <row r="30" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="169" t="s">
+      <c r="A30" s="132" t="s">
         <v>116</v>
       </c>
       <c r="B30" s="104" t="s">
@@ -4595,7 +4598,7 @@
       <c r="C30" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="D30" s="122">
+      <c r="D30" s="105">
         <v>5</v>
       </c>
     </row>
@@ -4609,7 +4612,7 @@
     <mergeCell ref="C6:C7"/>
     <mergeCell ref="D6:F6"/>
   </mergeCells>
-  <phoneticPr fontId="9" type="noConversion"/>
+  <phoneticPr fontId="10" type="noConversion"/>
   <hyperlinks>
     <hyperlink ref="B2" r:id="rId1" xr:uid="{EF9D475C-B1BB-4AC5-9EC0-B6DBBCF2F773}"/>
   </hyperlinks>
@@ -4656,13 +4659,13 @@
       <c r="C2" s="98"/>
     </row>
     <row r="3" spans="1:73" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="117" t="s">
+      <c r="A3" s="164" t="s">
         <v>98</v>
       </c>
-      <c r="B3" s="118"/>
-      <c r="C3" s="118"/>
-      <c r="D3" s="123"/>
-      <c r="E3" s="123"/>
+      <c r="B3" s="165"/>
+      <c r="C3" s="165"/>
+      <c r="D3" s="166"/>
+      <c r="E3" s="166"/>
     </row>
     <row r="4" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
@@ -4682,234 +4685,234 @@
       </c>
     </row>
     <row r="6" spans="1:73" ht="86.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="129" t="s">
+      <c r="A6" s="163" t="s">
         <v>85</v>
       </c>
-      <c r="B6" s="129" t="s">
+      <c r="B6" s="163" t="s">
         <v>86</v>
       </c>
-      <c r="C6" s="149" t="s">
+      <c r="C6" s="185" t="s">
         <v>87</v>
       </c>
-      <c r="D6" s="151" t="s">
+      <c r="D6" s="186" t="s">
         <v>128</v>
       </c>
-      <c r="E6" s="152"/>
-      <c r="F6" s="152"/>
-      <c r="G6" s="152" t="s">
+      <c r="E6" s="187"/>
+      <c r="F6" s="187"/>
+      <c r="G6" s="187" t="s">
         <v>129</v>
       </c>
-      <c r="H6" s="152"/>
-      <c r="I6" s="152"/>
-      <c r="J6" s="153" t="s">
+      <c r="H6" s="187"/>
+      <c r="I6" s="187"/>
+      <c r="J6" s="183" t="s">
         <v>162</v>
       </c>
-      <c r="K6" s="164" t="s">
+      <c r="K6" s="171" t="s">
         <v>154</v>
       </c>
-      <c r="L6" s="165"/>
-      <c r="M6" s="165"/>
-      <c r="N6" s="165"/>
-      <c r="O6" s="165"/>
-      <c r="P6" s="165"/>
-      <c r="Q6" s="165"/>
-      <c r="R6" s="166"/>
-      <c r="S6" s="164" t="s">
+      <c r="L6" s="172"/>
+      <c r="M6" s="172"/>
+      <c r="N6" s="172"/>
+      <c r="O6" s="172"/>
+      <c r="P6" s="172"/>
+      <c r="Q6" s="172"/>
+      <c r="R6" s="173"/>
+      <c r="S6" s="171" t="s">
         <v>152</v>
       </c>
-      <c r="T6" s="165"/>
-      <c r="U6" s="165"/>
-      <c r="V6" s="165"/>
-      <c r="W6" s="165"/>
-      <c r="X6" s="165"/>
-      <c r="Y6" s="165"/>
-      <c r="Z6" s="166"/>
-      <c r="AA6" s="164" t="s">
+      <c r="T6" s="172"/>
+      <c r="U6" s="172"/>
+      <c r="V6" s="172"/>
+      <c r="W6" s="172"/>
+      <c r="X6" s="172"/>
+      <c r="Y6" s="172"/>
+      <c r="Z6" s="173"/>
+      <c r="AA6" s="171" t="s">
         <v>153</v>
       </c>
-      <c r="AB6" s="165"/>
-      <c r="AC6" s="165"/>
-      <c r="AD6" s="165"/>
-      <c r="AE6" s="165"/>
-      <c r="AF6" s="165"/>
-      <c r="AG6" s="165"/>
-      <c r="AH6" s="166"/>
-      <c r="AI6" s="164" t="s">
+      <c r="AB6" s="172"/>
+      <c r="AC6" s="172"/>
+      <c r="AD6" s="172"/>
+      <c r="AE6" s="172"/>
+      <c r="AF6" s="172"/>
+      <c r="AG6" s="172"/>
+      <c r="AH6" s="173"/>
+      <c r="AI6" s="171" t="s">
         <v>151</v>
       </c>
-      <c r="AJ6" s="165"/>
-      <c r="AK6" s="165"/>
-      <c r="AL6" s="165"/>
-      <c r="AM6" s="165"/>
-      <c r="AN6" s="165"/>
-      <c r="AO6" s="165"/>
-      <c r="AP6" s="166"/>
-      <c r="AQ6" s="164" t="s">
+      <c r="AJ6" s="172"/>
+      <c r="AK6" s="172"/>
+      <c r="AL6" s="172"/>
+      <c r="AM6" s="172"/>
+      <c r="AN6" s="172"/>
+      <c r="AO6" s="172"/>
+      <c r="AP6" s="173"/>
+      <c r="AQ6" s="171" t="s">
         <v>149</v>
       </c>
-      <c r="AR6" s="165"/>
-      <c r="AS6" s="165"/>
-      <c r="AT6" s="165"/>
-      <c r="AU6" s="165"/>
-      <c r="AV6" s="165"/>
-      <c r="AW6" s="165"/>
-      <c r="AX6" s="166"/>
-      <c r="AY6" s="164" t="s">
+      <c r="AR6" s="172"/>
+      <c r="AS6" s="172"/>
+      <c r="AT6" s="172"/>
+      <c r="AU6" s="172"/>
+      <c r="AV6" s="172"/>
+      <c r="AW6" s="172"/>
+      <c r="AX6" s="173"/>
+      <c r="AY6" s="171" t="s">
         <v>150</v>
       </c>
-      <c r="AZ6" s="165"/>
-      <c r="BA6" s="165"/>
-      <c r="BB6" s="165"/>
-      <c r="BC6" s="165"/>
-      <c r="BD6" s="165"/>
-      <c r="BE6" s="165"/>
-      <c r="BF6" s="166"/>
-      <c r="BG6" s="164" t="s">
+      <c r="AZ6" s="172"/>
+      <c r="BA6" s="172"/>
+      <c r="BB6" s="172"/>
+      <c r="BC6" s="172"/>
+      <c r="BD6" s="172"/>
+      <c r="BE6" s="172"/>
+      <c r="BF6" s="173"/>
+      <c r="BG6" s="171" t="s">
         <v>155</v>
       </c>
-      <c r="BH6" s="165"/>
-      <c r="BI6" s="165"/>
-      <c r="BJ6" s="165"/>
-      <c r="BK6" s="165"/>
-      <c r="BL6" s="165"/>
-      <c r="BM6" s="165"/>
-      <c r="BN6" s="166"/>
-      <c r="BO6" s="178" t="s">
+      <c r="BH6" s="172"/>
+      <c r="BI6" s="172"/>
+      <c r="BJ6" s="172"/>
+      <c r="BK6" s="172"/>
+      <c r="BL6" s="172"/>
+      <c r="BM6" s="172"/>
+      <c r="BN6" s="173"/>
+      <c r="BO6" s="174" t="s">
         <v>156</v>
       </c>
-      <c r="BP6" s="179"/>
-      <c r="BQ6" s="179"/>
-      <c r="BR6" s="180"/>
-      <c r="BS6" s="160" t="s">
+      <c r="BP6" s="175"/>
+      <c r="BQ6" s="175"/>
+      <c r="BR6" s="176"/>
+      <c r="BS6" s="167" t="s">
         <v>158</v>
       </c>
-      <c r="BT6" s="161"/>
-      <c r="BU6" s="192" t="s">
+      <c r="BT6" s="168"/>
+      <c r="BU6" s="169" t="s">
         <v>161</v>
       </c>
     </row>
     <row r="7" spans="1:73" s="97" customFormat="1" ht="23.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="129"/>
-      <c r="B7" s="129"/>
-      <c r="C7" s="149"/>
-      <c r="D7" s="154" t="s">
+      <c r="A7" s="163"/>
+      <c r="B7" s="163"/>
+      <c r="C7" s="185"/>
+      <c r="D7" s="125" t="s">
         <v>114</v>
       </c>
-      <c r="E7" s="125" t="s">
+      <c r="E7" s="107" t="s">
         <v>115</v>
       </c>
-      <c r="F7" s="125" t="s">
+      <c r="F7" s="107" t="s">
         <v>116</v>
       </c>
-      <c r="G7" s="125" t="s">
+      <c r="G7" s="107" t="s">
         <v>114</v>
       </c>
-      <c r="H7" s="125" t="s">
+      <c r="H7" s="107" t="s">
         <v>115</v>
       </c>
-      <c r="I7" s="125" t="s">
+      <c r="I7" s="107" t="s">
         <v>116</v>
       </c>
-      <c r="J7" s="155"/>
-      <c r="K7" s="164" t="s">
+      <c r="J7" s="184"/>
+      <c r="K7" s="171" t="s">
         <v>17</v>
       </c>
-      <c r="L7" s="165"/>
-      <c r="M7" s="165"/>
-      <c r="N7" s="166"/>
-      <c r="O7" s="164" t="s">
+      <c r="L7" s="172"/>
+      <c r="M7" s="172"/>
+      <c r="N7" s="173"/>
+      <c r="O7" s="171" t="s">
         <v>18</v>
       </c>
-      <c r="P7" s="165"/>
-      <c r="Q7" s="165"/>
-      <c r="R7" s="166"/>
-      <c r="S7" s="164" t="s">
+      <c r="P7" s="172"/>
+      <c r="Q7" s="172"/>
+      <c r="R7" s="173"/>
+      <c r="S7" s="171" t="s">
         <v>17</v>
       </c>
-      <c r="T7" s="165"/>
-      <c r="U7" s="165"/>
-      <c r="V7" s="166"/>
-      <c r="W7" s="164" t="s">
+      <c r="T7" s="172"/>
+      <c r="U7" s="172"/>
+      <c r="V7" s="173"/>
+      <c r="W7" s="171" t="s">
         <v>18</v>
       </c>
-      <c r="X7" s="165"/>
-      <c r="Y7" s="165"/>
-      <c r="Z7" s="166"/>
-      <c r="AA7" s="164" t="s">
+      <c r="X7" s="172"/>
+      <c r="Y7" s="172"/>
+      <c r="Z7" s="173"/>
+      <c r="AA7" s="171" t="s">
         <v>17</v>
       </c>
-      <c r="AB7" s="165"/>
-      <c r="AC7" s="165"/>
-      <c r="AD7" s="166"/>
-      <c r="AE7" s="164" t="s">
+      <c r="AB7" s="172"/>
+      <c r="AC7" s="172"/>
+      <c r="AD7" s="173"/>
+      <c r="AE7" s="171" t="s">
         <v>18</v>
       </c>
-      <c r="AF7" s="165"/>
-      <c r="AG7" s="165"/>
-      <c r="AH7" s="166"/>
-      <c r="AI7" s="164" t="s">
+      <c r="AF7" s="172"/>
+      <c r="AG7" s="172"/>
+      <c r="AH7" s="173"/>
+      <c r="AI7" s="171" t="s">
         <v>17</v>
       </c>
-      <c r="AJ7" s="165"/>
-      <c r="AK7" s="165"/>
-      <c r="AL7" s="166"/>
-      <c r="AM7" s="164" t="s">
+      <c r="AJ7" s="172"/>
+      <c r="AK7" s="172"/>
+      <c r="AL7" s="173"/>
+      <c r="AM7" s="171" t="s">
         <v>18</v>
       </c>
-      <c r="AN7" s="165"/>
-      <c r="AO7" s="165"/>
-      <c r="AP7" s="166"/>
-      <c r="AQ7" s="164" t="s">
+      <c r="AN7" s="172"/>
+      <c r="AO7" s="172"/>
+      <c r="AP7" s="173"/>
+      <c r="AQ7" s="171" t="s">
         <v>17</v>
       </c>
-      <c r="AR7" s="165"/>
-      <c r="AS7" s="165"/>
-      <c r="AT7" s="166"/>
-      <c r="AU7" s="164" t="s">
+      <c r="AR7" s="172"/>
+      <c r="AS7" s="172"/>
+      <c r="AT7" s="173"/>
+      <c r="AU7" s="171" t="s">
         <v>18</v>
       </c>
-      <c r="AV7" s="165"/>
-      <c r="AW7" s="165"/>
-      <c r="AX7" s="166"/>
-      <c r="AY7" s="164" t="s">
+      <c r="AV7" s="172"/>
+      <c r="AW7" s="172"/>
+      <c r="AX7" s="173"/>
+      <c r="AY7" s="171" t="s">
         <v>17</v>
       </c>
-      <c r="AZ7" s="165"/>
-      <c r="BA7" s="165"/>
-      <c r="BB7" s="166"/>
-      <c r="BC7" s="164" t="s">
+      <c r="AZ7" s="172"/>
+      <c r="BA7" s="172"/>
+      <c r="BB7" s="173"/>
+      <c r="BC7" s="171" t="s">
         <v>18</v>
       </c>
-      <c r="BD7" s="165"/>
-      <c r="BE7" s="165"/>
-      <c r="BF7" s="166"/>
-      <c r="BG7" s="164" t="s">
+      <c r="BD7" s="172"/>
+      <c r="BE7" s="172"/>
+      <c r="BF7" s="173"/>
+      <c r="BG7" s="171" t="s">
         <v>17</v>
       </c>
-      <c r="BH7" s="165"/>
-      <c r="BI7" s="165"/>
-      <c r="BJ7" s="166"/>
-      <c r="BK7" s="164" t="s">
+      <c r="BH7" s="172"/>
+      <c r="BI7" s="172"/>
+      <c r="BJ7" s="173"/>
+      <c r="BK7" s="171" t="s">
         <v>18</v>
       </c>
-      <c r="BL7" s="165"/>
-      <c r="BM7" s="165"/>
-      <c r="BN7" s="166"/>
-      <c r="BO7" s="162" t="s">
+      <c r="BL7" s="172"/>
+      <c r="BM7" s="172"/>
+      <c r="BN7" s="173"/>
+      <c r="BO7" s="177" t="s">
         <v>157</v>
       </c>
-      <c r="BP7" s="163"/>
-      <c r="BQ7" s="162" t="s">
+      <c r="BP7" s="178"/>
+      <c r="BQ7" s="177" t="s">
         <v>26</v>
       </c>
-      <c r="BR7" s="190"/>
-      <c r="BS7" s="191" t="s">
+      <c r="BR7" s="179"/>
+      <c r="BS7" s="150" t="s">
         <v>159</v>
       </c>
-      <c r="BT7" s="191" t="s">
+      <c r="BT7" s="150" t="s">
         <v>160</v>
       </c>
-      <c r="BU7" s="193"/>
+      <c r="BU7" s="170"/>
     </row>
     <row r="8" spans="1:73" ht="30" x14ac:dyDescent="0.25">
       <c r="A8" s="102" t="s">
@@ -4918,28 +4921,28 @@
       <c r="B8" s="102" t="s">
         <v>84</v>
       </c>
-      <c r="C8" s="150" t="s">
+      <c r="C8" s="124" t="s">
         <v>72</v>
       </c>
-      <c r="D8" s="156" t="s">
+      <c r="D8" s="126" t="s">
         <v>104</v>
       </c>
-      <c r="E8" s="128" t="s">
+      <c r="E8" s="110" t="s">
         <v>105</v>
       </c>
-      <c r="F8" s="128" t="s">
+      <c r="F8" s="110" t="s">
         <v>104</v>
       </c>
-      <c r="G8" s="128">
-        <f>IF(D8=$A$21,$B$21,(IF(D8=$A$22,$B$22,IF(D8=$A$23,$B$23,$B$24))))</f>
+      <c r="G8" s="110">
+        <f t="shared" ref="G8:G17" si="0">IF(D8=$A$21,$B$21,(IF(D8=$A$22,$B$22,IF(D8=$A$23,$B$23,$B$24))))</f>
         <v>1</v>
       </c>
-      <c r="H8" s="128">
-        <f>IF(E8=$A$21,$B$21,(IF(E8=$A$22,$B$22,IF(E8=$A$23,$B$23,$B$24))))</f>
+      <c r="H8" s="110">
+        <f t="shared" ref="H8:H17" si="1">IF(E8=$A$21,$B$21,(IF(E8=$A$22,$B$22,IF(E8=$A$23,$B$23,$B$24))))</f>
         <v>0.66</v>
       </c>
-      <c r="I8" s="128">
-        <f>IF(F8=$A$21,$B$21,(IF(F8=$A$22,$B$22,IF(F8=$A$23,$B$23,$B$24))))</f>
+      <c r="I8" s="110">
+        <f t="shared" ref="I8:I17" si="2">IF(F8=$A$21,$B$21,(IF(F8=$A$22,$B$22,IF(F8=$A$23,$B$23,$B$24))))</f>
         <v>1</v>
       </c>
       <c r="J8" s="10">
@@ -5095,46 +5098,46 @@
         <v>7.5349999999999993</v>
       </c>
       <c r="BH8" s="83">
-        <f t="shared" ref="BH8:BN8" si="0">AJ8+AR8+AZ8</f>
+        <f t="shared" ref="BH8:BN8" si="3">AJ8+AR8+AZ8</f>
         <v>11.219999999999999</v>
       </c>
       <c r="BI8" s="83">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>15.81</v>
       </c>
       <c r="BJ8" s="83">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>20.295000000000002</v>
       </c>
       <c r="BK8" s="81">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>7.830000000000001</v>
       </c>
       <c r="BL8" s="83">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>11.219999999999999</v>
       </c>
       <c r="BM8" s="83">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>15.81</v>
       </c>
       <c r="BN8" s="83">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>18.82</v>
       </c>
-      <c r="BO8" s="181">
+      <c r="BO8" s="141">
         <f>BO$5*BH8+(1-BO$5)*BG8</f>
         <v>10.482999999999999</v>
       </c>
-      <c r="BP8" s="187">
+      <c r="BP8" s="147">
         <f>BO$5*BI8+(1-BO$5)*BJ8</f>
         <v>16.707000000000001</v>
       </c>
-      <c r="BQ8" s="181">
+      <c r="BQ8" s="141">
         <f>BO$5*BL8+(1-BO$5)*BK8</f>
         <v>10.541999999999998</v>
       </c>
-      <c r="BR8" s="182">
+      <c r="BR8" s="142">
         <f>BO$5*BM8+(1-BO$5)*BN8</f>
         <v>16.411999999999999</v>
       </c>
@@ -5146,7 +5149,7 @@
         <f>(BQ8+BR8)/2</f>
         <v>13.476999999999999</v>
       </c>
-      <c r="BU8" s="175">
+      <c r="BU8" s="138">
         <f>(BS8+BT8)/2</f>
         <v>13.535999999999998</v>
       </c>
@@ -5158,41 +5161,41 @@
       <c r="B9" s="102" t="s">
         <v>73</v>
       </c>
-      <c r="C9" s="150" t="s">
+      <c r="C9" s="124" t="s">
         <v>88</v>
       </c>
-      <c r="D9" s="156" t="s">
+      <c r="D9" s="126" t="s">
         <v>106</v>
       </c>
-      <c r="E9" s="128" t="s">
+      <c r="E9" s="110" t="s">
         <v>106</v>
       </c>
-      <c r="F9" s="128" t="s">
+      <c r="F9" s="110" t="s">
         <v>105</v>
       </c>
-      <c r="G9" s="128">
-        <f>IF(D9=$A$21,$B$21,(IF(D9=$A$22,$B$22,IF(D9=$A$23,$B$23,$B$24))))</f>
+      <c r="G9" s="110">
+        <f t="shared" si="0"/>
         <v>0.33</v>
       </c>
-      <c r="H9" s="128">
-        <f>IF(E9=$A$21,$B$21,(IF(E9=$A$22,$B$22,IF(E9=$A$23,$B$23,$B$24))))</f>
+      <c r="H9" s="110">
+        <f t="shared" si="1"/>
         <v>0.33</v>
       </c>
-      <c r="I9" s="128">
-        <f>IF(F9=$A$21,$B$21,(IF(F9=$A$22,$B$22,IF(F9=$A$23,$B$23,$B$24))))</f>
+      <c r="I9" s="110">
+        <f t="shared" si="2"/>
         <v>0.66</v>
       </c>
       <c r="J9" s="10">
-        <f t="shared" ref="J9:J17" si="1">G9*$D$35+H9*$D$36+I9*$D$37</f>
+        <f t="shared" ref="J9:J17" si="4">G9*$D$35+H9*$D$36+I9*$D$37</f>
         <v>6.6000000000000005</v>
       </c>
       <c r="K9" s="87">
         <v>0.11000000000000003</v>
       </c>
-      <c r="L9" s="131">
+      <c r="L9">
         <v>0.22000000000000003</v>
       </c>
-      <c r="M9" s="131">
+      <c r="M9">
         <v>0.44</v>
       </c>
       <c r="N9" s="88">
@@ -5201,10 +5204,10 @@
       <c r="O9" s="87">
         <v>0.14000000000000001</v>
       </c>
-      <c r="P9" s="131">
+      <c r="P9">
         <v>0.22000000000000003</v>
       </c>
-      <c r="Q9" s="131">
+      <c r="Q9">
         <v>0.44</v>
       </c>
       <c r="R9" s="88">
@@ -5213,10 +5216,10 @@
       <c r="S9" s="87">
         <v>0.11000000000000003</v>
       </c>
-      <c r="T9" s="131">
+      <c r="T9">
         <v>0.22000000000000003</v>
       </c>
-      <c r="U9" s="131">
+      <c r="U9">
         <v>0.44</v>
       </c>
       <c r="V9" s="88">
@@ -5225,10 +5228,10 @@
       <c r="W9" s="87">
         <v>0.14000000000000001</v>
       </c>
-      <c r="X9" s="131">
+      <c r="X9">
         <v>0.22000000000000003</v>
       </c>
-      <c r="Y9" s="131">
+      <c r="Y9">
         <v>0.44</v>
       </c>
       <c r="Z9" s="88">
@@ -5237,10 +5240,10 @@
       <c r="AA9" s="87">
         <v>0.44000000000000006</v>
       </c>
-      <c r="AB9" s="131">
+      <c r="AB9">
         <v>0.55000000000000004</v>
       </c>
-      <c r="AC9" s="131">
+      <c r="AC9">
         <v>0.77</v>
       </c>
       <c r="AD9" s="88">
@@ -5249,10 +5252,10 @@
       <c r="AE9" s="87">
         <v>0.47000000000000003</v>
       </c>
-      <c r="AF9" s="131">
+      <c r="AF9">
         <v>0.55000000000000004</v>
       </c>
-      <c r="AG9" s="131">
+      <c r="AG9">
         <v>0.77</v>
       </c>
       <c r="AH9" s="88">
@@ -5261,10 +5264,10 @@
       <c r="AI9" s="87">
         <v>0.44000000000000017</v>
       </c>
-      <c r="AJ9" s="131">
+      <c r="AJ9">
         <v>1.5400000000000003</v>
       </c>
-      <c r="AK9" s="131">
+      <c r="AK9">
         <v>3.52</v>
       </c>
       <c r="AL9" s="88">
@@ -5273,10 +5276,10 @@
       <c r="AM9" s="87">
         <v>0.76</v>
       </c>
-      <c r="AN9" s="131">
+      <c r="AN9">
         <v>1.5400000000000003</v>
       </c>
-      <c r="AO9" s="131">
+      <c r="AO9">
         <v>3.52</v>
       </c>
       <c r="AP9" s="88">
@@ -5285,22 +5288,22 @@
       <c r="AQ9" s="87">
         <v>-0.10999999999999999</v>
       </c>
-      <c r="AR9" s="131">
+      <c r="AR9">
         <v>0.44000000000000006</v>
       </c>
-      <c r="AS9" s="131">
+      <c r="AS9">
         <v>1.32</v>
       </c>
-      <c r="AT9" s="131">
+      <c r="AT9">
         <v>2.3099999999999996</v>
       </c>
       <c r="AU9" s="87">
         <v>5.9999999999999942E-2</v>
       </c>
-      <c r="AV9" s="131">
+      <c r="AV9">
         <v>0.44000000000000006</v>
       </c>
-      <c r="AW9" s="131">
+      <c r="AW9">
         <v>1.32</v>
       </c>
       <c r="AX9" s="88">
@@ -5309,85 +5312,85 @@
       <c r="AY9" s="87">
         <v>1.1550000000000002</v>
       </c>
-      <c r="AZ9" s="131">
+      <c r="AZ9">
         <v>2.4750000000000001</v>
       </c>
-      <c r="BA9" s="131">
+      <c r="BA9">
         <v>4.2350000000000003</v>
       </c>
-      <c r="BB9" s="131">
+      <c r="BB9">
         <v>5.9950000000000001</v>
       </c>
       <c r="BC9" s="87">
         <v>1.5650000000000008</v>
       </c>
-      <c r="BD9" s="131">
+      <c r="BD9">
         <v>2.4750000000000001</v>
       </c>
-      <c r="BE9" s="131">
+      <c r="BE9">
         <v>4.2350000000000003</v>
       </c>
       <c r="BF9" s="88">
         <v>5.4449999999999994</v>
       </c>
       <c r="BG9" s="87">
-        <f t="shared" ref="BG9:BG17" si="2">AI9+AQ9+AY9</f>
+        <f t="shared" ref="BG9:BG17" si="5">AI9+AQ9+AY9</f>
         <v>1.4850000000000003</v>
       </c>
-      <c r="BH9" s="131">
-        <f t="shared" ref="BH9:BH17" si="3">AJ9+AR9+AZ9</f>
+      <c r="BH9">
+        <f t="shared" ref="BH9:BH17" si="6">AJ9+AR9+AZ9</f>
         <v>4.4550000000000001</v>
       </c>
-      <c r="BI9" s="131">
-        <f t="shared" ref="BI9:BI17" si="4">AK9+AS9+BA9</f>
+      <c r="BI9">
+        <f t="shared" ref="BI9:BI17" si="7">AK9+AS9+BA9</f>
         <v>9.0749999999999993</v>
       </c>
-      <c r="BJ9" s="131">
-        <f t="shared" ref="BJ9:BJ17" si="5">AL9+AT9+BB9</f>
+      <c r="BJ9">
+        <f t="shared" ref="BJ9:BJ17" si="8">AL9+AT9+BB9</f>
         <v>13.365</v>
       </c>
       <c r="BK9" s="87">
-        <f t="shared" ref="BK9:BK17" si="6">AM9+AU9+BC9</f>
+        <f t="shared" ref="BK9:BK17" si="9">AM9+AU9+BC9</f>
         <v>2.3850000000000007</v>
       </c>
-      <c r="BL9" s="131">
-        <f t="shared" ref="BL9:BL17" si="7">AN9+AV9+BD9</f>
+      <c r="BL9">
+        <f t="shared" ref="BL9:BL17" si="10">AN9+AV9+BD9</f>
         <v>4.4550000000000001</v>
       </c>
-      <c r="BM9" s="131">
-        <f t="shared" ref="BM9:BM17" si="8">AO9+AW9+BE9</f>
+      <c r="BM9">
+        <f t="shared" ref="BM9:BM17" si="11">AO9+AW9+BE9</f>
         <v>9.0749999999999993</v>
       </c>
-      <c r="BN9" s="131">
-        <f t="shared" ref="BN9:BN17" si="9">AP9+AX9+BF9</f>
+      <c r="BN9">
+        <f t="shared" ref="BN9:BN17" si="12">AP9+AX9+BF9</f>
         <v>12.045000000000002</v>
       </c>
-      <c r="BO9" s="183">
-        <f t="shared" ref="BO9:BO17" si="10">BO$5*BH9+(1-BO$5)*BG9</f>
+      <c r="BO9" s="143">
+        <f t="shared" ref="BO9:BO17" si="13">BO$5*BH9+(1-BO$5)*BG9</f>
         <v>3.8610000000000002</v>
       </c>
-      <c r="BP9" s="188">
-        <f t="shared" ref="BP9:BP17" si="11">BO$5*BI9+(1-BO$5)*BJ9</f>
+      <c r="BP9" s="148">
+        <f t="shared" ref="BP9:BP17" si="14">BO$5*BI9+(1-BO$5)*BJ9</f>
         <v>9.9329999999999998</v>
       </c>
-      <c r="BQ9" s="183">
-        <f t="shared" ref="BQ9:BQ17" si="12">BO$5*BL9+(1-BO$5)*BK9</f>
+      <c r="BQ9" s="143">
+        <f t="shared" ref="BQ9:BQ17" si="15">BO$5*BL9+(1-BO$5)*BK9</f>
         <v>4.0410000000000004</v>
       </c>
-      <c r="BR9" s="184">
-        <f t="shared" ref="BR9:BR17" si="13">BO$5*BM9+(1-BO$5)*BN9</f>
+      <c r="BR9" s="144">
+        <f t="shared" ref="BR9:BR17" si="16">BO$5*BM9+(1-BO$5)*BN9</f>
         <v>9.6690000000000005</v>
       </c>
       <c r="BS9" s="87">
-        <f t="shared" ref="BS9:BS17" si="14">(BO9+BP9)/2</f>
+        <f t="shared" ref="BS9:BS17" si="17">(BO9+BP9)/2</f>
         <v>6.8970000000000002</v>
       </c>
       <c r="BT9" s="88">
-        <f t="shared" ref="BT9:BT17" si="15">(BQ9+BR9)/2</f>
+        <f t="shared" ref="BT9:BT17" si="18">(BQ9+BR9)/2</f>
         <v>6.8550000000000004</v>
       </c>
-      <c r="BU9" s="176">
-        <f t="shared" ref="BU9:BU18" si="16">(BS9+BT9)/2</f>
+      <c r="BU9" s="139">
+        <f t="shared" ref="BU9:BU17" si="19">(BS9+BT9)/2</f>
         <v>6.8760000000000003</v>
       </c>
     </row>
@@ -5398,41 +5401,41 @@
       <c r="B10" s="102" t="s">
         <v>74</v>
       </c>
-      <c r="C10" s="150" t="s">
+      <c r="C10" s="124" t="s">
         <v>89</v>
       </c>
-      <c r="D10" s="156" t="s">
+      <c r="D10" s="126" t="s">
         <v>105</v>
       </c>
-      <c r="E10" s="128" t="s">
+      <c r="E10" s="110" t="s">
         <v>105</v>
       </c>
-      <c r="F10" s="128" t="s">
+      <c r="F10" s="110" t="s">
         <v>105</v>
       </c>
-      <c r="G10" s="128">
-        <f>IF(D10=$A$21,$B$21,(IF(D10=$A$22,$B$22,IF(D10=$A$23,$B$23,$B$24))))</f>
+      <c r="G10" s="110">
+        <f t="shared" si="0"/>
         <v>0.66</v>
       </c>
-      <c r="H10" s="128">
-        <f>IF(E10=$A$21,$B$21,(IF(E10=$A$22,$B$22,IF(E10=$A$23,$B$23,$B$24))))</f>
+      <c r="H10" s="110">
+        <f t="shared" si="1"/>
         <v>0.66</v>
       </c>
-      <c r="I10" s="128">
-        <f>IF(F10=$A$21,$B$21,(IF(F10=$A$22,$B$22,IF(F10=$A$23,$B$23,$B$24))))</f>
+      <c r="I10" s="110">
+        <f t="shared" si="2"/>
         <v>0.66</v>
       </c>
       <c r="J10" s="10">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>9.9</v>
       </c>
       <c r="K10" s="87">
         <v>0.44000000000000006</v>
       </c>
-      <c r="L10" s="131">
+      <c r="L10">
         <v>0.55000000000000004</v>
       </c>
-      <c r="M10" s="131">
+      <c r="M10">
         <v>0.77</v>
       </c>
       <c r="N10" s="88">
@@ -5441,10 +5444,10 @@
       <c r="O10" s="87">
         <v>0.47000000000000003</v>
       </c>
-      <c r="P10" s="131">
+      <c r="P10">
         <v>0.55000000000000004</v>
       </c>
-      <c r="Q10" s="131">
+      <c r="Q10">
         <v>0.77</v>
       </c>
       <c r="R10" s="88">
@@ -5453,10 +5456,10 @@
       <c r="S10" s="87">
         <v>0.44000000000000006</v>
       </c>
-      <c r="T10" s="131">
+      <c r="T10">
         <v>0.55000000000000004</v>
       </c>
-      <c r="U10" s="131">
+      <c r="U10">
         <v>0.77</v>
       </c>
       <c r="V10" s="88">
@@ -5465,10 +5468,10 @@
       <c r="W10" s="87">
         <v>0.47000000000000003</v>
       </c>
-      <c r="X10" s="131">
+      <c r="X10">
         <v>0.55000000000000004</v>
       </c>
-      <c r="Y10" s="131">
+      <c r="Y10">
         <v>0.77</v>
       </c>
       <c r="Z10" s="88">
@@ -5477,10 +5480,10 @@
       <c r="AA10" s="87">
         <v>0.44000000000000006</v>
       </c>
-      <c r="AB10" s="131">
+      <c r="AB10">
         <v>0.55000000000000004</v>
       </c>
-      <c r="AC10" s="131">
+      <c r="AC10">
         <v>0.77</v>
       </c>
       <c r="AD10" s="88">
@@ -5489,10 +5492,10 @@
       <c r="AE10" s="87">
         <v>0.47000000000000003</v>
       </c>
-      <c r="AF10" s="131">
+      <c r="AF10">
         <v>0.55000000000000004</v>
       </c>
-      <c r="AG10" s="131">
+      <c r="AG10">
         <v>0.77</v>
       </c>
       <c r="AH10" s="88">
@@ -5501,10 +5504,10 @@
       <c r="AI10" s="87">
         <v>2.2549999999999999</v>
       </c>
-      <c r="AJ10" s="131">
+      <c r="AJ10">
         <v>3.8500000000000005</v>
       </c>
-      <c r="AK10" s="131">
+      <c r="AK10">
         <v>6.16</v>
       </c>
       <c r="AL10" s="88">
@@ -5513,10 +5516,10 @@
       <c r="AM10" s="87">
         <v>2.7399999999999993</v>
       </c>
-      <c r="AN10" s="131">
+      <c r="AN10">
         <v>3.8500000000000005</v>
       </c>
-      <c r="AO10" s="131">
+      <c r="AO10">
         <v>6.16</v>
       </c>
       <c r="AP10" s="88">
@@ -5525,22 +5528,22 @@
       <c r="AQ10" s="87">
         <v>5.500000000000016E-2</v>
       </c>
-      <c r="AR10" s="131">
+      <c r="AR10">
         <v>1.1000000000000001</v>
       </c>
-      <c r="AS10" s="131">
+      <c r="AS10">
         <v>2.31</v>
       </c>
-      <c r="AT10" s="131">
+      <c r="AT10">
         <v>3.7950000000000004</v>
       </c>
       <c r="AU10" s="87">
         <v>0.39000000000000012</v>
       </c>
-      <c r="AV10" s="131">
+      <c r="AV10">
         <v>1.1000000000000001</v>
       </c>
-      <c r="AW10" s="131">
+      <c r="AW10">
         <v>2.31</v>
       </c>
       <c r="AX10" s="88">
@@ -5549,85 +5552,85 @@
       <c r="AY10" s="87">
         <v>1.1550000000000002</v>
       </c>
-      <c r="AZ10" s="131">
+      <c r="AZ10">
         <v>2.4750000000000001</v>
       </c>
-      <c r="BA10" s="131">
+      <c r="BA10">
         <v>4.2350000000000003</v>
       </c>
-      <c r="BB10" s="131">
+      <c r="BB10">
         <v>5.9950000000000001</v>
       </c>
       <c r="BC10" s="87">
         <v>1.5650000000000008</v>
       </c>
-      <c r="BD10" s="131">
+      <c r="BD10">
         <v>2.4750000000000001</v>
       </c>
-      <c r="BE10" s="131">
+      <c r="BE10">
         <v>4.2350000000000003</v>
       </c>
       <c r="BF10" s="88">
         <v>5.4449999999999994</v>
       </c>
       <c r="BG10" s="87">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>3.4650000000000003</v>
       </c>
-      <c r="BH10" s="131">
-        <f t="shared" si="3"/>
+      <c r="BH10">
+        <f t="shared" si="6"/>
         <v>7.4250000000000007</v>
       </c>
-      <c r="BI10" s="131">
-        <f t="shared" si="4"/>
+      <c r="BI10">
+        <f t="shared" si="7"/>
         <v>12.705000000000002</v>
       </c>
-      <c r="BJ10" s="131">
-        <f t="shared" si="5"/>
+      <c r="BJ10">
+        <f t="shared" si="8"/>
         <v>17.984999999999999</v>
       </c>
       <c r="BK10" s="87">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>4.6950000000000003</v>
       </c>
-      <c r="BL10" s="131">
-        <f t="shared" si="7"/>
+      <c r="BL10">
+        <f t="shared" si="10"/>
         <v>7.4250000000000007</v>
       </c>
-      <c r="BM10" s="131">
-        <f t="shared" si="8"/>
+      <c r="BM10">
+        <f t="shared" si="11"/>
         <v>12.705000000000002</v>
       </c>
-      <c r="BN10" s="131">
-        <f t="shared" si="9"/>
+      <c r="BN10">
+        <f t="shared" si="12"/>
         <v>16.335000000000001</v>
       </c>
-      <c r="BO10" s="183">
-        <f t="shared" si="10"/>
+      <c r="BO10" s="143">
+        <f t="shared" si="13"/>
         <v>6.6330000000000009</v>
       </c>
-      <c r="BP10" s="188">
-        <f t="shared" si="11"/>
+      <c r="BP10" s="148">
+        <f t="shared" si="14"/>
         <v>13.761000000000001</v>
       </c>
-      <c r="BQ10" s="183">
-        <f t="shared" si="12"/>
+      <c r="BQ10" s="143">
+        <f t="shared" si="15"/>
         <v>6.8790000000000013</v>
       </c>
-      <c r="BR10" s="184">
-        <f t="shared" si="13"/>
+      <c r="BR10" s="144">
+        <f t="shared" si="16"/>
         <v>13.431000000000001</v>
       </c>
       <c r="BS10" s="87">
-        <f t="shared" si="14"/>
+        <f t="shared" si="17"/>
         <v>10.197000000000001</v>
       </c>
       <c r="BT10" s="88">
-        <f t="shared" si="15"/>
+        <f t="shared" si="18"/>
         <v>10.155000000000001</v>
       </c>
-      <c r="BU10" s="176">
-        <f t="shared" si="16"/>
+      <c r="BU10" s="139">
+        <f t="shared" si="19"/>
         <v>10.176000000000002</v>
       </c>
     </row>
@@ -5638,41 +5641,41 @@
       <c r="B11" s="102" t="s">
         <v>75</v>
       </c>
-      <c r="C11" s="150" t="s">
+      <c r="C11" s="124" t="s">
         <v>76</v>
       </c>
-      <c r="D11" s="156" t="s">
+      <c r="D11" s="126" t="s">
         <v>104</v>
       </c>
-      <c r="E11" s="128" t="s">
+      <c r="E11" s="110" t="s">
         <v>105</v>
       </c>
-      <c r="F11" s="128" t="s">
+      <c r="F11" s="110" t="s">
         <v>105</v>
       </c>
-      <c r="G11" s="128">
-        <f>IF(D11=$A$21,$B$21,(IF(D11=$A$22,$B$22,IF(D11=$A$23,$B$23,$B$24))))</f>
+      <c r="G11" s="110">
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="H11" s="128">
-        <f>IF(E11=$A$21,$B$21,(IF(E11=$A$22,$B$22,IF(E11=$A$23,$B$23,$B$24))))</f>
+      <c r="H11" s="110">
+        <f t="shared" si="1"/>
         <v>0.66</v>
       </c>
-      <c r="I11" s="128">
-        <f>IF(F11=$A$21,$B$21,(IF(F11=$A$22,$B$22,IF(F11=$A$23,$B$23,$B$24))))</f>
+      <c r="I11" s="110">
+        <f t="shared" si="2"/>
         <v>0.66</v>
       </c>
       <c r="J11" s="10">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>12.450000000000001</v>
       </c>
       <c r="K11" s="87">
         <v>0.88</v>
       </c>
-      <c r="L11" s="131">
+      <c r="L11">
         <v>0.88</v>
       </c>
-      <c r="M11" s="131">
+      <c r="M11">
         <v>1</v>
       </c>
       <c r="N11" s="88">
@@ -5681,10 +5684,10 @@
       <c r="O11" s="87">
         <v>0.8</v>
       </c>
-      <c r="P11" s="131">
+      <c r="P11">
         <v>0.88</v>
       </c>
-      <c r="Q11" s="131">
+      <c r="Q11">
         <v>1</v>
       </c>
       <c r="R11" s="88">
@@ -5693,10 +5696,10 @@
       <c r="S11" s="87">
         <v>0.44000000000000006</v>
       </c>
-      <c r="T11" s="131">
+      <c r="T11">
         <v>0.55000000000000004</v>
       </c>
-      <c r="U11" s="131">
+      <c r="U11">
         <v>0.77</v>
       </c>
       <c r="V11" s="88">
@@ -5705,10 +5708,10 @@
       <c r="W11" s="87">
         <v>0.47000000000000003</v>
       </c>
-      <c r="X11" s="131">
+      <c r="X11">
         <v>0.55000000000000004</v>
       </c>
-      <c r="Y11" s="131">
+      <c r="Y11">
         <v>0.77</v>
       </c>
       <c r="Z11" s="88">
@@ -5717,10 +5720,10 @@
       <c r="AA11" s="87">
         <v>0.44000000000000006</v>
       </c>
-      <c r="AB11" s="131">
+      <c r="AB11">
         <v>0.55000000000000004</v>
       </c>
-      <c r="AC11" s="131">
+      <c r="AC11">
         <v>0.77</v>
       </c>
       <c r="AD11" s="88">
@@ -5729,10 +5732,10 @@
       <c r="AE11" s="87">
         <v>0.47000000000000003</v>
       </c>
-      <c r="AF11" s="131">
+      <c r="AF11">
         <v>0.55000000000000004</v>
       </c>
-      <c r="AG11" s="131">
+      <c r="AG11">
         <v>0.77</v>
       </c>
       <c r="AH11" s="88">
@@ -5741,10 +5744,10 @@
       <c r="AI11" s="87">
         <v>4.84</v>
       </c>
-      <c r="AJ11" s="131">
+      <c r="AJ11">
         <v>6.16</v>
       </c>
-      <c r="AK11" s="131">
+      <c r="AK11">
         <v>8</v>
       </c>
       <c r="AL11" s="88">
@@ -5753,10 +5756,10 @@
       <c r="AM11" s="87">
         <v>4.7200000000000006</v>
       </c>
-      <c r="AN11" s="131">
+      <c r="AN11">
         <v>6.16</v>
       </c>
-      <c r="AO11" s="131">
+      <c r="AO11">
         <v>8</v>
       </c>
       <c r="AP11" s="88">
@@ -5765,22 +5768,22 @@
       <c r="AQ11" s="87">
         <v>5.500000000000016E-2</v>
       </c>
-      <c r="AR11" s="131">
+      <c r="AR11">
         <v>1.1000000000000001</v>
       </c>
-      <c r="AS11" s="131">
+      <c r="AS11">
         <v>2.31</v>
       </c>
-      <c r="AT11" s="131">
+      <c r="AT11">
         <v>3.7950000000000004</v>
       </c>
       <c r="AU11" s="87">
         <v>0.39000000000000012</v>
       </c>
-      <c r="AV11" s="131">
+      <c r="AV11">
         <v>1.1000000000000001</v>
       </c>
-      <c r="AW11" s="131">
+      <c r="AW11">
         <v>2.31</v>
       </c>
       <c r="AX11" s="88">
@@ -5789,85 +5792,85 @@
       <c r="AY11" s="87">
         <v>1.1550000000000002</v>
       </c>
-      <c r="AZ11" s="131">
+      <c r="AZ11">
         <v>2.4750000000000001</v>
       </c>
-      <c r="BA11" s="131">
+      <c r="BA11">
         <v>4.2350000000000003</v>
       </c>
-      <c r="BB11" s="131">
+      <c r="BB11">
         <v>5.9950000000000001</v>
       </c>
       <c r="BC11" s="87">
         <v>1.5650000000000008</v>
       </c>
-      <c r="BD11" s="131">
+      <c r="BD11">
         <v>2.4750000000000001</v>
       </c>
-      <c r="BE11" s="131">
+      <c r="BE11">
         <v>4.2350000000000003</v>
       </c>
       <c r="BF11" s="88">
         <v>5.4449999999999994</v>
       </c>
       <c r="BG11" s="87">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>6.05</v>
       </c>
-      <c r="BH11" s="131">
-        <f t="shared" si="3"/>
+      <c r="BH11">
+        <f t="shared" si="6"/>
         <v>9.7349999999999994</v>
       </c>
-      <c r="BI11" s="131">
-        <f t="shared" si="4"/>
+      <c r="BI11">
+        <f t="shared" si="7"/>
         <v>14.545000000000002</v>
       </c>
-      <c r="BJ11" s="131">
-        <f t="shared" si="5"/>
+      <c r="BJ11">
+        <f t="shared" si="8"/>
         <v>19.29</v>
       </c>
       <c r="BK11" s="87">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>6.6750000000000025</v>
       </c>
-      <c r="BL11" s="131">
-        <f t="shared" si="7"/>
+      <c r="BL11">
+        <f t="shared" si="10"/>
         <v>9.7349999999999994</v>
       </c>
-      <c r="BM11" s="131">
-        <f t="shared" si="8"/>
+      <c r="BM11">
+        <f t="shared" si="11"/>
         <v>14.545000000000002</v>
       </c>
-      <c r="BN11" s="131">
-        <f t="shared" si="9"/>
+      <c r="BN11">
+        <f t="shared" si="12"/>
         <v>17.765000000000001</v>
       </c>
-      <c r="BO11" s="183">
-        <f t="shared" si="10"/>
+      <c r="BO11" s="143">
+        <f t="shared" si="13"/>
         <v>8.9979999999999993</v>
       </c>
-      <c r="BP11" s="188">
-        <f t="shared" si="11"/>
+      <c r="BP11" s="148">
+        <f t="shared" si="14"/>
         <v>15.494000000000002</v>
       </c>
-      <c r="BQ11" s="183">
-        <f t="shared" si="12"/>
+      <c r="BQ11" s="143">
+        <f t="shared" si="15"/>
         <v>9.1230000000000011</v>
       </c>
-      <c r="BR11" s="184">
-        <f t="shared" si="13"/>
+      <c r="BR11" s="144">
+        <f t="shared" si="16"/>
         <v>15.189000000000002</v>
       </c>
       <c r="BS11" s="87">
-        <f t="shared" si="14"/>
+        <f t="shared" si="17"/>
         <v>12.246</v>
       </c>
       <c r="BT11" s="88">
-        <f t="shared" si="15"/>
+        <f t="shared" si="18"/>
         <v>12.156000000000002</v>
       </c>
-      <c r="BU11" s="176">
-        <f t="shared" si="16"/>
+      <c r="BU11" s="139">
+        <f t="shared" si="19"/>
         <v>12.201000000000001</v>
       </c>
     </row>
@@ -5878,41 +5881,41 @@
       <c r="B12" s="102" t="s">
         <v>77</v>
       </c>
-      <c r="C12" s="150" t="s">
+      <c r="C12" s="124" t="s">
         <v>90</v>
       </c>
-      <c r="D12" s="156" t="s">
+      <c r="D12" s="126" t="s">
         <v>105</v>
       </c>
-      <c r="E12" s="128" t="s">
+      <c r="E12" s="110" t="s">
         <v>104</v>
       </c>
-      <c r="F12" s="128" t="s">
+      <c r="F12" s="110" t="s">
         <v>105</v>
       </c>
-      <c r="G12" s="128">
-        <f>IF(D12=$A$21,$B$21,(IF(D12=$A$22,$B$22,IF(D12=$A$23,$B$23,$B$24))))</f>
+      <c r="G12" s="110">
+        <f t="shared" si="0"/>
         <v>0.66</v>
       </c>
-      <c r="H12" s="128">
-        <f>IF(E12=$A$21,$B$21,(IF(E12=$A$22,$B$22,IF(E12=$A$23,$B$23,$B$24))))</f>
+      <c r="H12" s="110">
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="I12" s="128">
-        <f>IF(F12=$A$21,$B$21,(IF(F12=$A$22,$B$22,IF(F12=$A$23,$B$23,$B$24))))</f>
+      <c r="I12" s="110">
+        <f t="shared" si="2"/>
         <v>0.66</v>
       </c>
       <c r="J12" s="10">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>10.75</v>
       </c>
       <c r="K12" s="87">
         <v>0.44000000000000006</v>
       </c>
-      <c r="L12" s="131">
+      <c r="L12">
         <v>0.55000000000000004</v>
       </c>
-      <c r="M12" s="131">
+      <c r="M12">
         <v>0.77</v>
       </c>
       <c r="N12" s="88">
@@ -5921,10 +5924,10 @@
       <c r="O12" s="87">
         <v>0.47000000000000003</v>
       </c>
-      <c r="P12" s="131">
+      <c r="P12">
         <v>0.55000000000000004</v>
       </c>
-      <c r="Q12" s="131">
+      <c r="Q12">
         <v>0.77</v>
       </c>
       <c r="R12" s="88">
@@ -5933,10 +5936,10 @@
       <c r="S12" s="87">
         <v>0.88</v>
       </c>
-      <c r="T12" s="131">
+      <c r="T12">
         <v>0.88</v>
       </c>
-      <c r="U12" s="131">
+      <c r="U12">
         <v>1</v>
       </c>
       <c r="V12" s="88">
@@ -5945,10 +5948,10 @@
       <c r="W12" s="87">
         <v>0.8</v>
       </c>
-      <c r="X12" s="131">
+      <c r="X12">
         <v>0.88</v>
       </c>
-      <c r="Y12" s="131">
+      <c r="Y12">
         <v>1</v>
       </c>
       <c r="Z12" s="88">
@@ -5957,10 +5960,10 @@
       <c r="AA12" s="87">
         <v>0.44000000000000006</v>
       </c>
-      <c r="AB12" s="131">
+      <c r="AB12">
         <v>0.55000000000000004</v>
       </c>
-      <c r="AC12" s="131">
+      <c r="AC12">
         <v>0.77</v>
       </c>
       <c r="AD12" s="88">
@@ -5969,10 +5972,10 @@
       <c r="AE12" s="87">
         <v>0.47000000000000003</v>
       </c>
-      <c r="AF12" s="131">
+      <c r="AF12">
         <v>0.55000000000000004</v>
       </c>
-      <c r="AG12" s="131">
+      <c r="AG12">
         <v>0.77</v>
       </c>
       <c r="AH12" s="88">
@@ -5981,10 +5984,10 @@
       <c r="AI12" s="87">
         <v>2.2549999999999999</v>
       </c>
-      <c r="AJ12" s="131">
+      <c r="AJ12">
         <v>3.8500000000000005</v>
       </c>
-      <c r="AK12" s="131">
+      <c r="AK12">
         <v>6.16</v>
       </c>
       <c r="AL12" s="88">
@@ -5993,10 +5996,10 @@
       <c r="AM12" s="87">
         <v>2.7399999999999993</v>
       </c>
-      <c r="AN12" s="131">
+      <c r="AN12">
         <v>3.8500000000000005</v>
       </c>
-      <c r="AO12" s="131">
+      <c r="AO12">
         <v>6.16</v>
       </c>
       <c r="AP12" s="88">
@@ -6005,22 +6008,22 @@
       <c r="AQ12" s="87">
         <v>0.44000000000000017</v>
       </c>
-      <c r="AR12" s="131">
+      <c r="AR12">
         <v>1.76</v>
       </c>
-      <c r="AS12" s="131">
+      <c r="AS12">
         <v>3</v>
       </c>
-      <c r="AT12" s="131">
+      <c r="AT12">
         <v>4.5</v>
       </c>
       <c r="AU12" s="87">
         <v>0.72</v>
       </c>
-      <c r="AV12" s="131">
+      <c r="AV12">
         <v>1.76</v>
       </c>
-      <c r="AW12" s="131">
+      <c r="AW12">
         <v>3</v>
       </c>
       <c r="AX12" s="88">
@@ -6029,85 +6032,85 @@
       <c r="AY12" s="87">
         <v>1.1550000000000002</v>
       </c>
-      <c r="AZ12" s="131">
+      <c r="AZ12">
         <v>2.4750000000000001</v>
       </c>
-      <c r="BA12" s="131">
+      <c r="BA12">
         <v>4.2350000000000003</v>
       </c>
-      <c r="BB12" s="131">
+      <c r="BB12">
         <v>5.9950000000000001</v>
       </c>
       <c r="BC12" s="87">
         <v>1.5650000000000008</v>
       </c>
-      <c r="BD12" s="131">
+      <c r="BD12">
         <v>2.4750000000000001</v>
       </c>
-      <c r="BE12" s="131">
+      <c r="BE12">
         <v>4.2350000000000003</v>
       </c>
       <c r="BF12" s="88">
         <v>5.4449999999999994</v>
       </c>
       <c r="BG12" s="87">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>3.8500000000000005</v>
       </c>
-      <c r="BH12" s="131">
-        <f t="shared" si="3"/>
+      <c r="BH12">
+        <f t="shared" si="6"/>
         <v>8.0850000000000009</v>
       </c>
-      <c r="BI12" s="131">
-        <f t="shared" si="4"/>
+      <c r="BI12">
+        <f t="shared" si="7"/>
         <v>13.395</v>
       </c>
-      <c r="BJ12" s="131">
-        <f t="shared" si="5"/>
+      <c r="BJ12">
+        <f t="shared" si="8"/>
         <v>18.690000000000001</v>
       </c>
       <c r="BK12" s="87">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>5.0250000000000004</v>
       </c>
-      <c r="BL12" s="131">
-        <f t="shared" si="7"/>
+      <c r="BL12">
+        <f t="shared" si="10"/>
         <v>8.0850000000000009</v>
       </c>
-      <c r="BM12" s="131">
-        <f t="shared" si="8"/>
+      <c r="BM12">
+        <f t="shared" si="11"/>
         <v>13.395</v>
       </c>
-      <c r="BN12" s="131">
-        <f t="shared" si="9"/>
+      <c r="BN12">
+        <f t="shared" si="12"/>
         <v>17.015000000000001</v>
       </c>
-      <c r="BO12" s="183">
-        <f t="shared" si="10"/>
+      <c r="BO12" s="143">
+        <f t="shared" si="13"/>
         <v>7.2380000000000004</v>
       </c>
-      <c r="BP12" s="188">
-        <f t="shared" si="11"/>
+      <c r="BP12" s="148">
+        <f t="shared" si="14"/>
         <v>14.454000000000001</v>
       </c>
-      <c r="BQ12" s="183">
-        <f t="shared" si="12"/>
+      <c r="BQ12" s="143">
+        <f t="shared" si="15"/>
         <v>7.4730000000000008</v>
       </c>
-      <c r="BR12" s="184">
-        <f t="shared" si="13"/>
+      <c r="BR12" s="144">
+        <f t="shared" si="16"/>
         <v>14.119</v>
       </c>
       <c r="BS12" s="87">
-        <f t="shared" si="14"/>
+        <f t="shared" si="17"/>
         <v>10.846</v>
       </c>
       <c r="BT12" s="88">
-        <f t="shared" si="15"/>
+        <f t="shared" si="18"/>
         <v>10.795999999999999</v>
       </c>
-      <c r="BU12" s="176">
-        <f t="shared" si="16"/>
+      <c r="BU12" s="139">
+        <f t="shared" si="19"/>
         <v>10.821</v>
       </c>
     </row>
@@ -6118,41 +6121,41 @@
       <c r="B13" s="102" t="s">
         <v>78</v>
       </c>
-      <c r="C13" s="150" t="s">
+      <c r="C13" s="124" t="s">
         <v>91</v>
       </c>
-      <c r="D13" s="156" t="s">
+      <c r="D13" s="126" t="s">
         <v>104</v>
       </c>
-      <c r="E13" s="128" t="s">
+      <c r="E13" s="110" t="s">
         <v>105</v>
       </c>
-      <c r="F13" s="128" t="s">
+      <c r="F13" s="110" t="s">
         <v>106</v>
       </c>
-      <c r="G13" s="128">
-        <f>IF(D13=$A$21,$B$21,(IF(D13=$A$22,$B$22,IF(D13=$A$23,$B$23,$B$24))))</f>
+      <c r="G13" s="110">
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="H13" s="128">
-        <f>IF(E13=$A$21,$B$21,(IF(E13=$A$22,$B$22,IF(E13=$A$23,$B$23,$B$24))))</f>
+      <c r="H13" s="110">
+        <f t="shared" si="1"/>
         <v>0.66</v>
       </c>
-      <c r="I13" s="128">
-        <f>IF(F13=$A$21,$B$21,(IF(F13=$A$22,$B$22,IF(F13=$A$23,$B$23,$B$24))))</f>
+      <c r="I13" s="110">
+        <f t="shared" si="2"/>
         <v>0.33</v>
       </c>
       <c r="J13" s="10">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>10.8</v>
       </c>
       <c r="K13" s="87">
         <v>0.88</v>
       </c>
-      <c r="L13" s="131">
+      <c r="L13">
         <v>0.88</v>
       </c>
-      <c r="M13" s="131">
+      <c r="M13">
         <v>1</v>
       </c>
       <c r="N13" s="88">
@@ -6161,10 +6164,10 @@
       <c r="O13" s="87">
         <v>0.8</v>
       </c>
-      <c r="P13" s="131">
+      <c r="P13">
         <v>0.88</v>
       </c>
-      <c r="Q13" s="131">
+      <c r="Q13">
         <v>1</v>
       </c>
       <c r="R13" s="88">
@@ -6173,10 +6176,10 @@
       <c r="S13" s="87">
         <v>0.44000000000000006</v>
       </c>
-      <c r="T13" s="131">
+      <c r="T13">
         <v>0.55000000000000004</v>
       </c>
-      <c r="U13" s="131">
+      <c r="U13">
         <v>0.77</v>
       </c>
       <c r="V13" s="88">
@@ -6185,10 +6188,10 @@
       <c r="W13" s="87">
         <v>0.47000000000000003</v>
       </c>
-      <c r="X13" s="131">
+      <c r="X13">
         <v>0.55000000000000004</v>
       </c>
-      <c r="Y13" s="131">
+      <c r="Y13">
         <v>0.77</v>
       </c>
       <c r="Z13" s="88">
@@ -6197,10 +6200,10 @@
       <c r="AA13" s="87">
         <v>0.11000000000000003</v>
       </c>
-      <c r="AB13" s="131">
+      <c r="AB13">
         <v>0.22000000000000003</v>
       </c>
-      <c r="AC13" s="131">
+      <c r="AC13">
         <v>0.44</v>
       </c>
       <c r="AD13" s="88">
@@ -6209,10 +6212,10 @@
       <c r="AE13" s="87">
         <v>0.14000000000000001</v>
       </c>
-      <c r="AF13" s="131">
+      <c r="AF13">
         <v>0.22000000000000003</v>
       </c>
-      <c r="AG13" s="131">
+      <c r="AG13">
         <v>0.44</v>
       </c>
       <c r="AH13" s="88">
@@ -6221,10 +6224,10 @@
       <c r="AI13" s="87">
         <v>4.84</v>
       </c>
-      <c r="AJ13" s="131">
+      <c r="AJ13">
         <v>6.16</v>
       </c>
-      <c r="AK13" s="131">
+      <c r="AK13">
         <v>8</v>
       </c>
       <c r="AL13" s="88">
@@ -6233,10 +6236,10 @@
       <c r="AM13" s="87">
         <v>4.7200000000000006</v>
       </c>
-      <c r="AN13" s="131">
+      <c r="AN13">
         <v>6.16</v>
       </c>
-      <c r="AO13" s="131">
+      <c r="AO13">
         <v>8</v>
       </c>
       <c r="AP13" s="88">
@@ -6245,22 +6248,22 @@
       <c r="AQ13" s="87">
         <v>5.500000000000016E-2</v>
       </c>
-      <c r="AR13" s="131">
+      <c r="AR13">
         <v>1.1000000000000001</v>
       </c>
-      <c r="AS13" s="131">
+      <c r="AS13">
         <v>2.31</v>
       </c>
-      <c r="AT13" s="131">
+      <c r="AT13">
         <v>3.7950000000000004</v>
       </c>
       <c r="AU13" s="87">
         <v>0.39000000000000012</v>
       </c>
-      <c r="AV13" s="131">
+      <c r="AV13">
         <v>1.1000000000000001</v>
       </c>
-      <c r="AW13" s="131">
+      <c r="AW13">
         <v>2.31</v>
       </c>
       <c r="AX13" s="88">
@@ -6269,85 +6272,85 @@
       <c r="AY13" s="87">
         <v>0.16500000000000015</v>
       </c>
-      <c r="AZ13" s="131">
+      <c r="AZ13">
         <v>0.9900000000000001</v>
       </c>
-      <c r="BA13" s="131">
+      <c r="BA13">
         <v>2.42</v>
       </c>
-      <c r="BB13" s="131">
+      <c r="BB13">
         <v>3.6850000000000005</v>
       </c>
       <c r="BC13" s="87">
         <v>0.41000000000000025</v>
       </c>
-      <c r="BD13" s="131">
+      <c r="BD13">
         <v>0.9900000000000001</v>
       </c>
-      <c r="BE13" s="131">
+      <c r="BE13">
         <v>2.42</v>
       </c>
       <c r="BF13" s="88">
         <v>3.3000000000000007</v>
       </c>
       <c r="BG13" s="87">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>5.0599999999999996</v>
       </c>
-      <c r="BH13" s="131">
-        <f t="shared" si="3"/>
+      <c r="BH13">
+        <f t="shared" si="6"/>
         <v>8.25</v>
       </c>
-      <c r="BI13" s="131">
-        <f t="shared" si="4"/>
+      <c r="BI13">
+        <f t="shared" si="7"/>
         <v>12.73</v>
       </c>
-      <c r="BJ13" s="131">
-        <f t="shared" si="5"/>
+      <c r="BJ13">
+        <f t="shared" si="8"/>
         <v>16.98</v>
       </c>
       <c r="BK13" s="87">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>5.5200000000000014</v>
       </c>
-      <c r="BL13" s="131">
-        <f t="shared" si="7"/>
+      <c r="BL13">
+        <f t="shared" si="10"/>
         <v>8.25</v>
       </c>
-      <c r="BM13" s="131">
-        <f t="shared" si="8"/>
+      <c r="BM13">
+        <f t="shared" si="11"/>
         <v>12.73</v>
       </c>
-      <c r="BN13" s="131">
-        <f t="shared" si="9"/>
+      <c r="BN13">
+        <f t="shared" si="12"/>
         <v>15.620000000000001</v>
       </c>
-      <c r="BO13" s="183">
-        <f t="shared" si="10"/>
+      <c r="BO13" s="143">
+        <f t="shared" si="13"/>
         <v>7.6120000000000001</v>
       </c>
-      <c r="BP13" s="188">
-        <f t="shared" si="11"/>
+      <c r="BP13" s="148">
+        <f t="shared" si="14"/>
         <v>13.58</v>
       </c>
-      <c r="BQ13" s="183">
-        <f t="shared" si="12"/>
+      <c r="BQ13" s="143">
+        <f t="shared" si="15"/>
         <v>7.7040000000000006</v>
       </c>
-      <c r="BR13" s="184">
-        <f t="shared" si="13"/>
+      <c r="BR13" s="144">
+        <f t="shared" si="16"/>
         <v>13.308</v>
       </c>
       <c r="BS13" s="87">
-        <f t="shared" si="14"/>
+        <f t="shared" si="17"/>
         <v>10.596</v>
       </c>
       <c r="BT13" s="88">
-        <f t="shared" si="15"/>
+        <f t="shared" si="18"/>
         <v>10.506</v>
       </c>
-      <c r="BU13" s="176">
-        <f t="shared" si="16"/>
+      <c r="BU13" s="139">
+        <f t="shared" si="19"/>
         <v>10.551</v>
       </c>
     </row>
@@ -6358,41 +6361,41 @@
       <c r="B14" s="102" t="s">
         <v>79</v>
       </c>
-      <c r="C14" s="150" t="s">
+      <c r="C14" s="124" t="s">
         <v>92</v>
       </c>
-      <c r="D14" s="156" t="s">
+      <c r="D14" s="126" t="s">
         <v>104</v>
       </c>
-      <c r="E14" s="128" t="s">
+      <c r="E14" s="110" t="s">
         <v>105</v>
       </c>
-      <c r="F14" s="128" t="s">
+      <c r="F14" s="110" t="s">
         <v>106</v>
       </c>
-      <c r="G14" s="128">
-        <f>IF(D14=$A$21,$B$21,(IF(D14=$A$22,$B$22,IF(D14=$A$23,$B$23,$B$24))))</f>
+      <c r="G14" s="110">
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="H14" s="128">
-        <f>IF(E14=$A$21,$B$21,(IF(E14=$A$22,$B$22,IF(E14=$A$23,$B$23,$B$24))))</f>
+      <c r="H14" s="110">
+        <f t="shared" si="1"/>
         <v>0.66</v>
       </c>
-      <c r="I14" s="128">
-        <f>IF(F14=$A$21,$B$21,(IF(F14=$A$22,$B$22,IF(F14=$A$23,$B$23,$B$24))))</f>
+      <c r="I14" s="110">
+        <f t="shared" si="2"/>
         <v>0.33</v>
       </c>
       <c r="J14" s="10">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>10.8</v>
       </c>
       <c r="K14" s="87">
         <v>0.88</v>
       </c>
-      <c r="L14" s="131">
+      <c r="L14">
         <v>0.88</v>
       </c>
-      <c r="M14" s="131">
+      <c r="M14">
         <v>1</v>
       </c>
       <c r="N14" s="88">
@@ -6401,10 +6404,10 @@
       <c r="O14" s="87">
         <v>0.8</v>
       </c>
-      <c r="P14" s="131">
+      <c r="P14">
         <v>0.88</v>
       </c>
-      <c r="Q14" s="131">
+      <c r="Q14">
         <v>1</v>
       </c>
       <c r="R14" s="88">
@@ -6413,10 +6416,10 @@
       <c r="S14" s="87">
         <v>0.44000000000000006</v>
       </c>
-      <c r="T14" s="131">
+      <c r="T14">
         <v>0.55000000000000004</v>
       </c>
-      <c r="U14" s="131">
+      <c r="U14">
         <v>0.77</v>
       </c>
       <c r="V14" s="88">
@@ -6425,10 +6428,10 @@
       <c r="W14" s="87">
         <v>0.47000000000000003</v>
       </c>
-      <c r="X14" s="131">
+      <c r="X14">
         <v>0.55000000000000004</v>
       </c>
-      <c r="Y14" s="131">
+      <c r="Y14">
         <v>0.77</v>
       </c>
       <c r="Z14" s="88">
@@ -6437,10 +6440,10 @@
       <c r="AA14" s="87">
         <v>0.11000000000000003</v>
       </c>
-      <c r="AB14" s="131">
+      <c r="AB14">
         <v>0.22000000000000003</v>
       </c>
-      <c r="AC14" s="131">
+      <c r="AC14">
         <v>0.44</v>
       </c>
       <c r="AD14" s="88">
@@ -6449,10 +6452,10 @@
       <c r="AE14" s="87">
         <v>0.14000000000000001</v>
       </c>
-      <c r="AF14" s="131">
+      <c r="AF14">
         <v>0.22000000000000003</v>
       </c>
-      <c r="AG14" s="131">
+      <c r="AG14">
         <v>0.44</v>
       </c>
       <c r="AH14" s="88">
@@ -6461,10 +6464,10 @@
       <c r="AI14" s="87">
         <v>4.84</v>
       </c>
-      <c r="AJ14" s="131">
+      <c r="AJ14">
         <v>6.16</v>
       </c>
-      <c r="AK14" s="131">
+      <c r="AK14">
         <v>8</v>
       </c>
       <c r="AL14" s="88">
@@ -6473,10 +6476,10 @@
       <c r="AM14" s="87">
         <v>4.7200000000000006</v>
       </c>
-      <c r="AN14" s="131">
+      <c r="AN14">
         <v>6.16</v>
       </c>
-      <c r="AO14" s="131">
+      <c r="AO14">
         <v>8</v>
       </c>
       <c r="AP14" s="88">
@@ -6485,22 +6488,22 @@
       <c r="AQ14" s="87">
         <v>5.500000000000016E-2</v>
       </c>
-      <c r="AR14" s="131">
+      <c r="AR14">
         <v>1.1000000000000001</v>
       </c>
-      <c r="AS14" s="131">
+      <c r="AS14">
         <v>2.31</v>
       </c>
-      <c r="AT14" s="131">
+      <c r="AT14">
         <v>3.7950000000000004</v>
       </c>
       <c r="AU14" s="87">
         <v>0.39000000000000012</v>
       </c>
-      <c r="AV14" s="131">
+      <c r="AV14">
         <v>1.1000000000000001</v>
       </c>
-      <c r="AW14" s="131">
+      <c r="AW14">
         <v>2.31</v>
       </c>
       <c r="AX14" s="88">
@@ -6509,85 +6512,85 @@
       <c r="AY14" s="87">
         <v>0.16500000000000015</v>
       </c>
-      <c r="AZ14" s="131">
+      <c r="AZ14">
         <v>0.9900000000000001</v>
       </c>
-      <c r="BA14" s="131">
+      <c r="BA14">
         <v>2.42</v>
       </c>
-      <c r="BB14" s="131">
+      <c r="BB14">
         <v>3.6850000000000005</v>
       </c>
       <c r="BC14" s="87">
         <v>0.41000000000000025</v>
       </c>
-      <c r="BD14" s="131">
+      <c r="BD14">
         <v>0.9900000000000001</v>
       </c>
-      <c r="BE14" s="131">
+      <c r="BE14">
         <v>2.42</v>
       </c>
       <c r="BF14" s="88">
         <v>3.3000000000000007</v>
       </c>
       <c r="BG14" s="87">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>5.0599999999999996</v>
       </c>
-      <c r="BH14" s="131">
-        <f t="shared" si="3"/>
+      <c r="BH14">
+        <f t="shared" si="6"/>
         <v>8.25</v>
       </c>
-      <c r="BI14" s="131">
-        <f t="shared" si="4"/>
+      <c r="BI14">
+        <f t="shared" si="7"/>
         <v>12.73</v>
       </c>
-      <c r="BJ14" s="131">
-        <f t="shared" si="5"/>
+      <c r="BJ14">
+        <f t="shared" si="8"/>
         <v>16.98</v>
       </c>
       <c r="BK14" s="87">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>5.5200000000000014</v>
       </c>
-      <c r="BL14" s="131">
-        <f t="shared" si="7"/>
+      <c r="BL14">
+        <f t="shared" si="10"/>
         <v>8.25</v>
       </c>
-      <c r="BM14" s="131">
-        <f t="shared" si="8"/>
+      <c r="BM14">
+        <f t="shared" si="11"/>
         <v>12.73</v>
       </c>
-      <c r="BN14" s="131">
-        <f t="shared" si="9"/>
+      <c r="BN14">
+        <f t="shared" si="12"/>
         <v>15.620000000000001</v>
       </c>
-      <c r="BO14" s="183">
-        <f t="shared" si="10"/>
+      <c r="BO14" s="143">
+        <f t="shared" si="13"/>
         <v>7.6120000000000001</v>
       </c>
-      <c r="BP14" s="188">
-        <f t="shared" si="11"/>
+      <c r="BP14" s="148">
+        <f t="shared" si="14"/>
         <v>13.58</v>
       </c>
-      <c r="BQ14" s="183">
-        <f t="shared" si="12"/>
+      <c r="BQ14" s="143">
+        <f t="shared" si="15"/>
         <v>7.7040000000000006</v>
       </c>
-      <c r="BR14" s="184">
-        <f t="shared" si="13"/>
+      <c r="BR14" s="144">
+        <f t="shared" si="16"/>
         <v>13.308</v>
       </c>
       <c r="BS14" s="87">
-        <f t="shared" si="14"/>
+        <f t="shared" si="17"/>
         <v>10.596</v>
       </c>
       <c r="BT14" s="88">
-        <f t="shared" si="15"/>
+        <f t="shared" si="18"/>
         <v>10.506</v>
       </c>
-      <c r="BU14" s="176">
-        <f t="shared" si="16"/>
+      <c r="BU14" s="139">
+        <f t="shared" si="19"/>
         <v>10.551</v>
       </c>
     </row>
@@ -6598,41 +6601,41 @@
       <c r="B15" s="102" t="s">
         <v>80</v>
       </c>
-      <c r="C15" s="150" t="s">
+      <c r="C15" s="124" t="s">
         <v>81</v>
       </c>
-      <c r="D15" s="156" t="s">
+      <c r="D15" s="126" t="s">
         <v>105</v>
       </c>
-      <c r="E15" s="128" t="s">
+      <c r="E15" s="110" t="s">
         <v>104</v>
       </c>
-      <c r="F15" s="128" t="s">
+      <c r="F15" s="110" t="s">
         <v>104</v>
       </c>
-      <c r="G15" s="128">
-        <f>IF(D15=$A$21,$B$21,(IF(D15=$A$22,$B$22,IF(D15=$A$23,$B$23,$B$24))))</f>
+      <c r="G15" s="110">
+        <f t="shared" si="0"/>
         <v>0.66</v>
       </c>
-      <c r="H15" s="128">
-        <f>IF(E15=$A$21,$B$21,(IF(E15=$A$22,$B$22,IF(E15=$A$23,$B$23,$B$24))))</f>
+      <c r="H15" s="110">
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="I15" s="128">
-        <f>IF(F15=$A$21,$B$21,(IF(F15=$A$22,$B$22,IF(F15=$A$23,$B$23,$B$24))))</f>
+      <c r="I15" s="110">
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="J15" s="10">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>12.45</v>
       </c>
       <c r="K15" s="87">
         <v>0.44000000000000006</v>
       </c>
-      <c r="L15" s="131">
+      <c r="L15">
         <v>0.55000000000000004</v>
       </c>
-      <c r="M15" s="131">
+      <c r="M15">
         <v>0.77</v>
       </c>
       <c r="N15" s="88">
@@ -6641,10 +6644,10 @@
       <c r="O15" s="87">
         <v>0.47000000000000003</v>
       </c>
-      <c r="P15" s="131">
+      <c r="P15">
         <v>0.55000000000000004</v>
       </c>
-      <c r="Q15" s="131">
+      <c r="Q15">
         <v>0.77</v>
       </c>
       <c r="R15" s="88">
@@ -6653,10 +6656,10 @@
       <c r="S15" s="87">
         <v>0.88</v>
       </c>
-      <c r="T15" s="131">
+      <c r="T15">
         <v>0.88</v>
       </c>
-      <c r="U15" s="131">
+      <c r="U15">
         <v>1</v>
       </c>
       <c r="V15" s="88">
@@ -6665,10 +6668,10 @@
       <c r="W15" s="87">
         <v>0.8</v>
       </c>
-      <c r="X15" s="131">
+      <c r="X15">
         <v>0.88</v>
       </c>
-      <c r="Y15" s="131">
+      <c r="Y15">
         <v>1</v>
       </c>
       <c r="Z15" s="88">
@@ -6677,10 +6680,10 @@
       <c r="AA15" s="87">
         <v>0.88</v>
       </c>
-      <c r="AB15" s="131">
+      <c r="AB15">
         <v>0.88</v>
       </c>
-      <c r="AC15" s="131">
+      <c r="AC15">
         <v>1</v>
       </c>
       <c r="AD15" s="88">
@@ -6689,10 +6692,10 @@
       <c r="AE15" s="87">
         <v>0.8</v>
       </c>
-      <c r="AF15" s="131">
+      <c r="AF15">
         <v>0.88</v>
       </c>
-      <c r="AG15" s="131">
+      <c r="AG15">
         <v>1</v>
       </c>
       <c r="AH15" s="88">
@@ -6701,10 +6704,10 @@
       <c r="AI15" s="87">
         <v>2.2549999999999999</v>
       </c>
-      <c r="AJ15" s="131">
+      <c r="AJ15">
         <v>3.8500000000000005</v>
       </c>
-      <c r="AK15" s="131">
+      <c r="AK15">
         <v>6.16</v>
       </c>
       <c r="AL15" s="88">
@@ -6713,10 +6716,10 @@
       <c r="AM15" s="87">
         <v>2.7399999999999993</v>
       </c>
-      <c r="AN15" s="131">
+      <c r="AN15">
         <v>3.8500000000000005</v>
       </c>
-      <c r="AO15" s="131">
+      <c r="AO15">
         <v>6.16</v>
       </c>
       <c r="AP15" s="88">
@@ -6725,22 +6728,22 @@
       <c r="AQ15" s="87">
         <v>0.44000000000000017</v>
       </c>
-      <c r="AR15" s="131">
+      <c r="AR15">
         <v>1.76</v>
       </c>
-      <c r="AS15" s="131">
+      <c r="AS15">
         <v>3</v>
       </c>
-      <c r="AT15" s="131">
+      <c r="AT15">
         <v>4.5</v>
       </c>
       <c r="AU15" s="87">
         <v>0.72</v>
       </c>
-      <c r="AV15" s="131">
+      <c r="AV15">
         <v>1.76</v>
       </c>
-      <c r="AW15" s="131">
+      <c r="AW15">
         <v>3</v>
       </c>
       <c r="AX15" s="88">
@@ -6749,85 +6752,85 @@
       <c r="AY15" s="87">
         <v>2.6399999999999997</v>
       </c>
-      <c r="AZ15" s="131">
+      <c r="AZ15">
         <v>3.96</v>
       </c>
-      <c r="BA15" s="131">
+      <c r="BA15">
         <v>5.5</v>
       </c>
-      <c r="BB15" s="131">
+      <c r="BB15">
         <v>7</v>
       </c>
       <c r="BC15" s="87">
         <v>2.7199999999999998</v>
       </c>
-      <c r="BD15" s="131">
+      <c r="BD15">
         <v>3.96</v>
       </c>
-      <c r="BE15" s="131">
+      <c r="BE15">
         <v>5.5</v>
       </c>
       <c r="BF15" s="88">
         <v>6.5</v>
       </c>
       <c r="BG15" s="87">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>5.335</v>
       </c>
-      <c r="BH15" s="131">
-        <f t="shared" si="3"/>
+      <c r="BH15">
+        <f t="shared" si="6"/>
         <v>9.57</v>
       </c>
-      <c r="BI15" s="131">
-        <f t="shared" si="4"/>
+      <c r="BI15">
+        <f t="shared" si="7"/>
         <v>14.66</v>
       </c>
-      <c r="BJ15" s="131">
-        <f t="shared" si="5"/>
+      <c r="BJ15">
+        <f t="shared" si="8"/>
         <v>19.695</v>
       </c>
       <c r="BK15" s="87">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>6.1799999999999988</v>
       </c>
-      <c r="BL15" s="131">
-        <f t="shared" si="7"/>
+      <c r="BL15">
+        <f t="shared" si="10"/>
         <v>9.57</v>
       </c>
-      <c r="BM15" s="131">
-        <f t="shared" si="8"/>
+      <c r="BM15">
+        <f t="shared" si="11"/>
         <v>14.66</v>
       </c>
-      <c r="BN15" s="131">
-        <f t="shared" si="9"/>
+      <c r="BN15">
+        <f t="shared" si="12"/>
         <v>18.07</v>
       </c>
-      <c r="BO15" s="183">
-        <f t="shared" si="10"/>
+      <c r="BO15" s="143">
+        <f t="shared" si="13"/>
         <v>8.7230000000000008</v>
       </c>
-      <c r="BP15" s="188">
-        <f t="shared" si="11"/>
+      <c r="BP15" s="148">
+        <f t="shared" si="14"/>
         <v>15.667000000000002</v>
       </c>
-      <c r="BQ15" s="183">
-        <f t="shared" si="12"/>
+      <c r="BQ15" s="143">
+        <f t="shared" si="15"/>
         <v>8.8919999999999995</v>
       </c>
-      <c r="BR15" s="184">
-        <f t="shared" si="13"/>
+      <c r="BR15" s="144">
+        <f t="shared" si="16"/>
         <v>15.342000000000001</v>
       </c>
       <c r="BS15" s="87">
-        <f t="shared" si="14"/>
+        <f t="shared" si="17"/>
         <v>12.195</v>
       </c>
       <c r="BT15" s="88">
-        <f t="shared" si="15"/>
+        <f t="shared" si="18"/>
         <v>12.117000000000001</v>
       </c>
-      <c r="BU15" s="176">
-        <f t="shared" si="16"/>
+      <c r="BU15" s="139">
+        <f t="shared" si="19"/>
         <v>12.156000000000001</v>
       </c>
     </row>
@@ -6838,41 +6841,41 @@
       <c r="B16" s="102" t="s">
         <v>82</v>
       </c>
-      <c r="C16" s="150" t="s">
+      <c r="C16" s="124" t="s">
         <v>93</v>
       </c>
-      <c r="D16" s="156" t="s">
+      <c r="D16" s="126" t="s">
         <v>105</v>
       </c>
-      <c r="E16" s="128" t="s">
+      <c r="E16" s="110" t="s">
         <v>104</v>
       </c>
-      <c r="F16" s="128" t="s">
+      <c r="F16" s="110" t="s">
         <v>105</v>
       </c>
-      <c r="G16" s="128">
-        <f>IF(D16=$A$21,$B$21,(IF(D16=$A$22,$B$22,IF(D16=$A$23,$B$23,$B$24))))</f>
+      <c r="G16" s="110">
+        <f t="shared" si="0"/>
         <v>0.66</v>
       </c>
-      <c r="H16" s="128">
-        <f>IF(E16=$A$21,$B$21,(IF(E16=$A$22,$B$22,IF(E16=$A$23,$B$23,$B$24))))</f>
+      <c r="H16" s="110">
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="I16" s="128">
-        <f>IF(F16=$A$21,$B$21,(IF(F16=$A$22,$B$22,IF(F16=$A$23,$B$23,$B$24))))</f>
+      <c r="I16" s="110">
+        <f t="shared" si="2"/>
         <v>0.66</v>
       </c>
       <c r="J16" s="10">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>10.75</v>
       </c>
       <c r="K16" s="87">
         <v>0.44000000000000006</v>
       </c>
-      <c r="L16" s="131">
+      <c r="L16">
         <v>0.55000000000000004</v>
       </c>
-      <c r="M16" s="131">
+      <c r="M16">
         <v>0.77</v>
       </c>
       <c r="N16" s="88">
@@ -6881,10 +6884,10 @@
       <c r="O16" s="87">
         <v>0.47000000000000003</v>
       </c>
-      <c r="P16" s="131">
+      <c r="P16">
         <v>0.55000000000000004</v>
       </c>
-      <c r="Q16" s="131">
+      <c r="Q16">
         <v>0.77</v>
       </c>
       <c r="R16" s="88">
@@ -6893,10 +6896,10 @@
       <c r="S16" s="87">
         <v>0.88</v>
       </c>
-      <c r="T16" s="131">
+      <c r="T16">
         <v>0.88</v>
       </c>
-      <c r="U16" s="131">
+      <c r="U16">
         <v>1</v>
       </c>
       <c r="V16" s="88">
@@ -6905,10 +6908,10 @@
       <c r="W16" s="87">
         <v>0.8</v>
       </c>
-      <c r="X16" s="131">
+      <c r="X16">
         <v>0.88</v>
       </c>
-      <c r="Y16" s="131">
+      <c r="Y16">
         <v>1</v>
       </c>
       <c r="Z16" s="88">
@@ -6917,10 +6920,10 @@
       <c r="AA16" s="87">
         <v>0.44000000000000006</v>
       </c>
-      <c r="AB16" s="131">
+      <c r="AB16">
         <v>0.55000000000000004</v>
       </c>
-      <c r="AC16" s="131">
+      <c r="AC16">
         <v>0.77</v>
       </c>
       <c r="AD16" s="88">
@@ -6929,10 +6932,10 @@
       <c r="AE16" s="87">
         <v>0.47000000000000003</v>
       </c>
-      <c r="AF16" s="131">
+      <c r="AF16">
         <v>0.55000000000000004</v>
       </c>
-      <c r="AG16" s="131">
+      <c r="AG16">
         <v>0.77</v>
       </c>
       <c r="AH16" s="88">
@@ -6941,10 +6944,10 @@
       <c r="AI16" s="87">
         <v>2.2549999999999999</v>
       </c>
-      <c r="AJ16" s="131">
+      <c r="AJ16">
         <v>3.8500000000000005</v>
       </c>
-      <c r="AK16" s="131">
+      <c r="AK16">
         <v>6.16</v>
       </c>
       <c r="AL16" s="88">
@@ -6953,10 +6956,10 @@
       <c r="AM16" s="87">
         <v>2.7399999999999993</v>
       </c>
-      <c r="AN16" s="131">
+      <c r="AN16">
         <v>3.8500000000000005</v>
       </c>
-      <c r="AO16" s="131">
+      <c r="AO16">
         <v>6.16</v>
       </c>
       <c r="AP16" s="88">
@@ -6965,22 +6968,22 @@
       <c r="AQ16" s="87">
         <v>0.44000000000000017</v>
       </c>
-      <c r="AR16" s="131">
+      <c r="AR16">
         <v>1.76</v>
       </c>
-      <c r="AS16" s="131">
+      <c r="AS16">
         <v>3</v>
       </c>
-      <c r="AT16" s="131">
+      <c r="AT16">
         <v>4.5</v>
       </c>
       <c r="AU16" s="87">
         <v>0.72</v>
       </c>
-      <c r="AV16" s="131">
+      <c r="AV16">
         <v>1.76</v>
       </c>
-      <c r="AW16" s="131">
+      <c r="AW16">
         <v>3</v>
       </c>
       <c r="AX16" s="88">
@@ -6989,85 +6992,85 @@
       <c r="AY16" s="87">
         <v>1.1550000000000002</v>
       </c>
-      <c r="AZ16" s="131">
+      <c r="AZ16">
         <v>2.4750000000000001</v>
       </c>
-      <c r="BA16" s="131">
+      <c r="BA16">
         <v>4.2350000000000003</v>
       </c>
-      <c r="BB16" s="131">
+      <c r="BB16">
         <v>5.9950000000000001</v>
       </c>
       <c r="BC16" s="87">
         <v>1.5650000000000008</v>
       </c>
-      <c r="BD16" s="131">
+      <c r="BD16">
         <v>2.4750000000000001</v>
       </c>
-      <c r="BE16" s="131">
+      <c r="BE16">
         <v>4.2350000000000003</v>
       </c>
       <c r="BF16" s="88">
         <v>5.4449999999999994</v>
       </c>
       <c r="BG16" s="87">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>3.8500000000000005</v>
       </c>
-      <c r="BH16" s="131">
-        <f t="shared" si="3"/>
+      <c r="BH16">
+        <f t="shared" si="6"/>
         <v>8.0850000000000009</v>
       </c>
-      <c r="BI16" s="131">
-        <f t="shared" si="4"/>
+      <c r="BI16">
+        <f t="shared" si="7"/>
         <v>13.395</v>
       </c>
-      <c r="BJ16" s="131">
-        <f t="shared" si="5"/>
+      <c r="BJ16">
+        <f t="shared" si="8"/>
         <v>18.690000000000001</v>
       </c>
       <c r="BK16" s="87">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>5.0250000000000004</v>
       </c>
-      <c r="BL16" s="131">
-        <f t="shared" si="7"/>
+      <c r="BL16">
+        <f t="shared" si="10"/>
         <v>8.0850000000000009</v>
       </c>
-      <c r="BM16" s="131">
-        <f t="shared" si="8"/>
+      <c r="BM16">
+        <f t="shared" si="11"/>
         <v>13.395</v>
       </c>
-      <c r="BN16" s="131">
-        <f t="shared" si="9"/>
+      <c r="BN16">
+        <f t="shared" si="12"/>
         <v>17.015000000000001</v>
       </c>
-      <c r="BO16" s="183">
-        <f t="shared" si="10"/>
+      <c r="BO16" s="143">
+        <f t="shared" si="13"/>
         <v>7.2380000000000004</v>
       </c>
-      <c r="BP16" s="188">
-        <f t="shared" si="11"/>
+      <c r="BP16" s="148">
+        <f t="shared" si="14"/>
         <v>14.454000000000001</v>
       </c>
-      <c r="BQ16" s="183">
-        <f t="shared" si="12"/>
+      <c r="BQ16" s="143">
+        <f t="shared" si="15"/>
         <v>7.4730000000000008</v>
       </c>
-      <c r="BR16" s="184">
-        <f t="shared" si="13"/>
+      <c r="BR16" s="144">
+        <f t="shared" si="16"/>
         <v>14.119</v>
       </c>
       <c r="BS16" s="87">
-        <f t="shared" si="14"/>
+        <f t="shared" si="17"/>
         <v>10.846</v>
       </c>
       <c r="BT16" s="88">
-        <f t="shared" si="15"/>
+        <f t="shared" si="18"/>
         <v>10.795999999999999</v>
       </c>
-      <c r="BU16" s="176">
-        <f t="shared" si="16"/>
+      <c r="BU16" s="139">
+        <f t="shared" si="19"/>
         <v>10.821</v>
       </c>
     </row>
@@ -7078,32 +7081,32 @@
       <c r="B17" s="102" t="s">
         <v>83</v>
       </c>
-      <c r="C17" s="150" t="s">
+      <c r="C17" s="124" t="s">
         <v>94</v>
       </c>
-      <c r="D17" s="157" t="s">
+      <c r="D17" s="127" t="s">
         <v>106</v>
       </c>
-      <c r="E17" s="158" t="s">
+      <c r="E17" s="128" t="s">
         <v>104</v>
       </c>
-      <c r="F17" s="158" t="s">
+      <c r="F17" s="128" t="s">
         <v>105</v>
       </c>
-      <c r="G17" s="158">
-        <f>IF(D17=$A$21,$B$21,(IF(D17=$A$22,$B$22,IF(D17=$A$23,$B$23,$B$24))))</f>
+      <c r="G17" s="128">
+        <f t="shared" si="0"/>
         <v>0.33</v>
       </c>
-      <c r="H17" s="158">
-        <f>IF(E17=$A$21,$B$21,(IF(E17=$A$22,$B$22,IF(E17=$A$23,$B$23,$B$24))))</f>
+      <c r="H17" s="128">
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="I17" s="158">
-        <f>IF(F17=$A$21,$B$21,(IF(F17=$A$22,$B$22,IF(F17=$A$23,$B$23,$B$24))))</f>
+      <c r="I17" s="128">
+        <f t="shared" si="2"/>
         <v>0.66</v>
       </c>
-      <c r="J17" s="159">
-        <f t="shared" si="1"/>
+      <c r="J17" s="129">
+        <f t="shared" si="4"/>
         <v>8.2750000000000004</v>
       </c>
       <c r="K17" s="91">
@@ -7251,63 +7254,63 @@
         <v>5.4449999999999994</v>
       </c>
       <c r="BG17" s="91">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>2.0350000000000006</v>
       </c>
       <c r="BH17" s="93">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>5.7750000000000004</v>
       </c>
       <c r="BI17" s="93">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>10.754999999999999</v>
       </c>
       <c r="BJ17" s="93">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>15.555</v>
       </c>
       <c r="BK17" s="91">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>3.0450000000000008</v>
       </c>
       <c r="BL17" s="93">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>5.7750000000000004</v>
       </c>
       <c r="BM17" s="93">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>10.754999999999999</v>
       </c>
       <c r="BN17" s="93">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v>14.045000000000002</v>
       </c>
-      <c r="BO17" s="185">
-        <f t="shared" si="10"/>
+      <c r="BO17" s="145">
+        <f t="shared" si="13"/>
         <v>5.0270000000000001</v>
       </c>
-      <c r="BP17" s="189">
-        <f t="shared" si="11"/>
+      <c r="BP17" s="149">
+        <f t="shared" si="14"/>
         <v>11.714999999999998</v>
       </c>
-      <c r="BQ17" s="185">
-        <f t="shared" si="12"/>
+      <c r="BQ17" s="145">
+        <f t="shared" si="15"/>
         <v>5.2290000000000001</v>
       </c>
-      <c r="BR17" s="186">
-        <f t="shared" si="13"/>
+      <c r="BR17" s="146">
+        <f t="shared" si="16"/>
         <v>11.412999999999998</v>
       </c>
       <c r="BS17" s="91">
-        <f t="shared" si="14"/>
+        <f t="shared" si="17"/>
         <v>8.3709999999999987</v>
       </c>
       <c r="BT17" s="94">
-        <f t="shared" si="15"/>
+        <f t="shared" si="18"/>
         <v>8.3209999999999997</v>
       </c>
-      <c r="BU17" s="177">
-        <f t="shared" si="16"/>
+      <c r="BU17" s="140">
+        <f t="shared" si="19"/>
         <v>8.3460000000000001</v>
       </c>
     </row>
@@ -7320,19 +7323,19 @@
       <c r="BK18" s="59"/>
     </row>
     <row r="19" spans="1:73" x14ac:dyDescent="0.25">
-      <c r="A19" s="132" t="s">
+      <c r="A19" s="1" t="s">
         <v>125</v>
       </c>
       <c r="B19" s="1"/>
     </row>
     <row r="20" spans="1:73" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="125" t="s">
+      <c r="A20" s="107" t="s">
         <v>103</v>
       </c>
-      <c r="B20" s="126" t="s">
+      <c r="B20" s="108" t="s">
         <v>123</v>
       </c>
-      <c r="E20" s="134" t="s">
+      <c r="E20" s="112" t="s">
         <v>17</v>
       </c>
       <c r="I20" t="s">
@@ -7340,7 +7343,7 @@
       </c>
     </row>
     <row r="21" spans="1:73" x14ac:dyDescent="0.25">
-      <c r="A21" s="124" t="s">
+      <c r="A21" s="106" t="s">
         <v>107</v>
       </c>
       <c r="B21" s="2">
@@ -7384,7 +7387,7 @@
       </c>
     </row>
     <row r="22" spans="1:73" x14ac:dyDescent="0.25">
-      <c r="A22" s="124" t="s">
+      <c r="A22" s="106" t="s">
         <v>106</v>
       </c>
       <c r="B22" s="2">
@@ -7400,37 +7403,37 @@
         <f>F22-0.11</f>
         <v>0.11000000000000003</v>
       </c>
-      <c r="F22" s="133">
+      <c r="F22" s="111">
         <f>C22-0.11</f>
         <v>0.22000000000000003</v>
       </c>
-      <c r="G22" s="131">
+      <c r="G22">
         <f>C22+0.11</f>
         <v>0.44</v>
       </c>
       <c r="H22" s="88">
-        <f t="shared" ref="H22:H23" si="17">G22+0.11</f>
+        <f t="shared" ref="H22:H23" si="20">G22+0.11</f>
         <v>0.55000000000000004</v>
       </c>
       <c r="I22" s="89">
         <f>J22-0.08</f>
         <v>0.14000000000000001</v>
       </c>
-      <c r="J22" s="131">
-        <f t="shared" ref="J22:K24" si="18">F22</f>
+      <c r="J22">
+        <f t="shared" ref="J22:K24" si="21">F22</f>
         <v>0.22000000000000003</v>
       </c>
-      <c r="K22" s="131">
-        <f t="shared" si="18"/>
+      <c r="K22">
+        <f t="shared" si="21"/>
         <v>0.44</v>
       </c>
       <c r="L22" s="90">
-        <f t="shared" ref="L22:L23" si="19">K22+0.08</f>
+        <f t="shared" ref="L22:L23" si="22">K22+0.08</f>
         <v>0.52</v>
       </c>
     </row>
     <row r="23" spans="1:73" x14ac:dyDescent="0.25">
-      <c r="A23" s="124" t="s">
+      <c r="A23" s="106" t="s">
         <v>105</v>
       </c>
       <c r="B23" s="2">
@@ -7443,40 +7446,40 @@
         <v>105</v>
       </c>
       <c r="E23" s="87">
-        <f t="shared" ref="E23" si="20">F23-0.11</f>
+        <f t="shared" ref="E23" si="23">F23-0.11</f>
         <v>0.44000000000000006</v>
       </c>
-      <c r="F23" s="133">
-        <f t="shared" ref="F23" si="21">C23-0.11</f>
+      <c r="F23" s="111">
+        <f t="shared" ref="F23" si="24">C23-0.11</f>
         <v>0.55000000000000004</v>
       </c>
-      <c r="G23" s="131">
-        <f t="shared" ref="G23" si="22">C23+0.11</f>
+      <c r="G23">
+        <f t="shared" ref="G23" si="25">C23+0.11</f>
         <v>0.77</v>
       </c>
       <c r="H23" s="88">
-        <f t="shared" si="17"/>
+        <f t="shared" si="20"/>
         <v>0.88</v>
       </c>
       <c r="I23" s="89">
-        <f t="shared" ref="I23:I24" si="23">J23-0.08</f>
+        <f t="shared" ref="I23:I24" si="26">J23-0.08</f>
         <v>0.47000000000000003</v>
       </c>
-      <c r="J23" s="131">
-        <f t="shared" si="18"/>
+      <c r="J23">
+        <f t="shared" si="21"/>
         <v>0.55000000000000004</v>
       </c>
-      <c r="K23" s="131">
-        <f t="shared" si="18"/>
+      <c r="K23">
+        <f t="shared" si="21"/>
         <v>0.77</v>
       </c>
       <c r="L23" s="90">
-        <f t="shared" si="19"/>
+        <f t="shared" si="22"/>
         <v>0.85</v>
       </c>
     </row>
     <row r="24" spans="1:73" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="124" t="s">
+      <c r="A24" s="106" t="s">
         <v>104</v>
       </c>
       <c r="B24" s="2">
@@ -7501,15 +7504,15 @@
         <v>1</v>
       </c>
       <c r="I24" s="95">
-        <f t="shared" si="23"/>
+        <f t="shared" si="26"/>
         <v>0.8</v>
       </c>
       <c r="J24" s="93">
-        <f t="shared" si="18"/>
+        <f t="shared" si="21"/>
         <v>0.88</v>
       </c>
       <c r="K24" s="93">
-        <f t="shared" si="18"/>
+        <f t="shared" si="21"/>
         <v>1</v>
       </c>
       <c r="L24" s="96">
@@ -7517,22 +7520,21 @@
       </c>
     </row>
     <row r="25" spans="1:73" x14ac:dyDescent="0.25">
-      <c r="A25" s="130"/>
-      <c r="B25" s="131"/>
+      <c r="A25" s="99"/>
     </row>
     <row r="26" spans="1:73" x14ac:dyDescent="0.25">
-      <c r="A26" s="132" t="s">
+      <c r="A26" s="1" t="s">
         <v>119</v>
       </c>
     </row>
     <row r="27" spans="1:73" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="125" t="s">
+      <c r="A27" s="107" t="s">
         <v>103</v>
       </c>
-      <c r="B27" s="126" t="s">
+      <c r="B27" s="108" t="s">
         <v>124</v>
       </c>
-      <c r="E27" s="134" t="s">
+      <c r="E27" s="112" t="s">
         <v>17</v>
       </c>
       <c r="I27" t="s">
@@ -7540,7 +7542,7 @@
       </c>
     </row>
     <row r="28" spans="1:73" x14ac:dyDescent="0.25">
-      <c r="A28" s="124" t="s">
+      <c r="A28" s="106" t="s">
         <v>107</v>
       </c>
       <c r="B28" s="2">
@@ -7584,7 +7586,7 @@
       </c>
     </row>
     <row r="29" spans="1:73" x14ac:dyDescent="0.25">
-      <c r="A29" s="124" t="s">
+      <c r="A29" s="106" t="s">
         <v>106</v>
       </c>
       <c r="B29" s="2">
@@ -7600,37 +7602,37 @@
         <f>F29-1.5</f>
         <v>0.5</v>
       </c>
-      <c r="F29" s="133">
+      <c r="F29" s="111">
         <f>C29-0.5</f>
         <v>2</v>
       </c>
-      <c r="G29" s="131">
+      <c r="G29">
         <f>C29+0.5</f>
         <v>3</v>
       </c>
       <c r="H29" s="88">
-        <f t="shared" ref="H29:H31" si="24">G29+1.5</f>
+        <f t="shared" ref="H29:H31" si="27">G29+1.5</f>
         <v>4.5</v>
       </c>
       <c r="I29" s="89">
         <f>J29-1</f>
         <v>1</v>
       </c>
-      <c r="J29" s="131">
-        <f t="shared" ref="J29:K31" si="25">F29</f>
+      <c r="J29">
+        <f t="shared" ref="J29:K31" si="28">F29</f>
         <v>2</v>
       </c>
-      <c r="K29" s="131">
-        <f t="shared" si="25"/>
+      <c r="K29">
+        <f t="shared" si="28"/>
         <v>3</v>
       </c>
       <c r="L29" s="90">
-        <f t="shared" ref="L29:L31" si="26">K29+1</f>
+        <f t="shared" ref="L29:L31" si="29">K29+1</f>
         <v>4</v>
       </c>
     </row>
     <row r="30" spans="1:73" x14ac:dyDescent="0.25">
-      <c r="A30" s="124" t="s">
+      <c r="A30" s="106" t="s">
         <v>105</v>
       </c>
       <c r="B30" s="2">
@@ -7643,40 +7645,40 @@
         <v>105</v>
       </c>
       <c r="E30" s="87">
-        <f t="shared" ref="E30:E31" si="27">F30-1.5</f>
+        <f t="shared" ref="E30:E31" si="30">F30-1.5</f>
         <v>3</v>
       </c>
-      <c r="F30" s="133">
+      <c r="F30" s="111">
         <f>C30-0.5</f>
         <v>4.5</v>
       </c>
-      <c r="G30" s="131">
+      <c r="G30">
         <f>C30+0.5</f>
         <v>5.5</v>
       </c>
       <c r="H30" s="88">
-        <f t="shared" si="24"/>
+        <f t="shared" si="27"/>
         <v>7</v>
       </c>
       <c r="I30" s="89">
-        <f t="shared" ref="I30:I31" si="28">J30-1</f>
+        <f t="shared" ref="I30:I31" si="31">J30-1</f>
         <v>3.5</v>
       </c>
-      <c r="J30" s="131">
-        <f t="shared" si="25"/>
+      <c r="J30">
+        <f t="shared" si="28"/>
         <v>4.5</v>
       </c>
-      <c r="K30" s="131">
-        <f t="shared" si="25"/>
+      <c r="K30">
+        <f t="shared" si="28"/>
         <v>5.5</v>
       </c>
       <c r="L30" s="90">
-        <f t="shared" si="26"/>
+        <f t="shared" si="29"/>
         <v>6.5</v>
       </c>
     </row>
     <row r="31" spans="1:73" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="124" t="s">
+      <c r="A31" s="106" t="s">
         <v>104</v>
       </c>
       <c r="B31" s="2">
@@ -7689,7 +7691,7 @@
         <v>104</v>
       </c>
       <c r="E31" s="91">
-        <f t="shared" si="27"/>
+        <f t="shared" si="30"/>
         <v>5.5</v>
       </c>
       <c r="F31" s="92">
@@ -7701,75 +7703,75 @@
         <v>8</v>
       </c>
       <c r="H31" s="94">
-        <f t="shared" si="24"/>
+        <f t="shared" si="27"/>
         <v>9.5</v>
       </c>
       <c r="I31" s="95">
+        <f t="shared" si="31"/>
+        <v>6</v>
+      </c>
+      <c r="J31" s="93">
         <f t="shared" si="28"/>
-        <v>6</v>
-      </c>
-      <c r="J31" s="93">
-        <f t="shared" si="25"/>
         <v>7</v>
       </c>
       <c r="K31" s="93">
-        <f t="shared" si="25"/>
+        <f t="shared" si="28"/>
         <v>8</v>
       </c>
       <c r="L31" s="96">
-        <f t="shared" si="26"/>
+        <f t="shared" si="29"/>
         <v>9</v>
       </c>
     </row>
     <row r="33" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="132" t="s">
+      <c r="A33" s="1" t="s">
         <v>120</v>
       </c>
     </row>
     <row r="34" spans="1:12" ht="67.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="138" t="s">
+      <c r="A34" s="114" t="s">
         <v>117</v>
       </c>
-      <c r="B34" s="139" t="s">
+      <c r="B34" s="113" t="s">
         <v>99</v>
       </c>
-      <c r="C34" s="140" t="s">
+      <c r="C34" s="115" t="s">
         <v>108</v>
       </c>
-      <c r="D34" s="141" t="s">
+      <c r="D34" s="116" t="s">
         <v>126</v>
       </c>
-      <c r="E34" s="135" t="s">
+      <c r="E34" s="180" t="s">
         <v>127</v>
       </c>
-      <c r="F34" s="136"/>
-      <c r="G34" s="136"/>
-      <c r="H34" s="136"/>
-      <c r="I34" s="136"/>
-      <c r="J34" s="136"/>
-      <c r="K34" s="136"/>
-      <c r="L34" s="137"/>
+      <c r="F34" s="181"/>
+      <c r="G34" s="181"/>
+      <c r="H34" s="181"/>
+      <c r="I34" s="181"/>
+      <c r="J34" s="181"/>
+      <c r="K34" s="181"/>
+      <c r="L34" s="182"/>
     </row>
     <row r="35" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A35" s="167" t="s">
+      <c r="A35" s="130" t="s">
         <v>114</v>
       </c>
-      <c r="B35" s="142" t="s">
+      <c r="B35" s="117" t="s">
         <v>100</v>
       </c>
-      <c r="C35" s="143" t="s">
+      <c r="C35" s="118" t="s">
         <v>104</v>
       </c>
-      <c r="D35" s="144">
+      <c r="D35" s="119">
         <v>7.5</v>
       </c>
       <c r="E35" s="87">
         <v>5.5</v>
       </c>
-      <c r="F35" s="133">
+      <c r="F35" s="111">
         <v>7</v>
       </c>
-      <c r="G35" s="131">
+      <c r="G35">
         <v>8</v>
       </c>
       <c r="H35" s="88">
@@ -7778,10 +7780,10 @@
       <c r="I35" s="89">
         <v>6</v>
       </c>
-      <c r="J35" s="131">
+      <c r="J35">
         <v>7</v>
       </c>
-      <c r="K35" s="131">
+      <c r="K35">
         <v>8</v>
       </c>
       <c r="L35" s="90">
@@ -7789,7 +7791,7 @@
       </c>
     </row>
     <row r="36" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A36" s="168" t="s">
+      <c r="A36" s="131" t="s">
         <v>115</v>
       </c>
       <c r="B36" s="104" t="s">
@@ -7798,16 +7800,16 @@
       <c r="C36" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="D36" s="145">
+      <c r="D36" s="120">
         <v>2.5</v>
       </c>
       <c r="E36" s="87">
         <v>0.5</v>
       </c>
-      <c r="F36" s="133">
+      <c r="F36" s="111">
         <v>2</v>
       </c>
-      <c r="G36" s="131">
+      <c r="G36">
         <v>3</v>
       </c>
       <c r="H36" s="88">
@@ -7816,10 +7818,10 @@
       <c r="I36" s="89">
         <v>1</v>
       </c>
-      <c r="J36" s="131">
+      <c r="J36">
         <v>2</v>
       </c>
-      <c r="K36" s="131">
+      <c r="K36">
         <v>3</v>
       </c>
       <c r="L36" s="90">
@@ -7827,16 +7829,16 @@
       </c>
     </row>
     <row r="37" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="169" t="s">
+      <c r="A37" s="132" t="s">
         <v>116</v>
       </c>
-      <c r="B37" s="146" t="s">
+      <c r="B37" s="121" t="s">
         <v>102</v>
       </c>
-      <c r="C37" s="147" t="s">
+      <c r="C37" s="122" t="s">
         <v>105</v>
       </c>
-      <c r="D37" s="148">
+      <c r="D37" s="123">
         <v>5</v>
       </c>
       <c r="E37" s="91">
@@ -7865,36 +7867,36 @@
       </c>
     </row>
     <row r="39" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="132" t="s">
+      <c r="A39" s="1" t="s">
         <v>130</v>
       </c>
     </row>
     <row r="40" spans="1:12" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="170" t="s">
+      <c r="A40" s="133" t="s">
         <v>134</v>
       </c>
-      <c r="B40" s="171" t="s">
+      <c r="B40" s="134" t="s">
         <v>135</v>
       </c>
-      <c r="E40" s="135" t="s">
+      <c r="E40" s="180" t="s">
         <v>136</v>
       </c>
-      <c r="F40" s="136"/>
-      <c r="G40" s="136"/>
-      <c r="H40" s="136"/>
-      <c r="I40" s="136"/>
-      <c r="J40" s="136"/>
-      <c r="K40" s="136"/>
-      <c r="L40" s="137"/>
+      <c r="F40" s="181"/>
+      <c r="G40" s="181"/>
+      <c r="H40" s="181"/>
+      <c r="I40" s="181"/>
+      <c r="J40" s="181"/>
+      <c r="K40" s="181"/>
+      <c r="L40" s="182"/>
     </row>
     <row r="41" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A41" s="167" t="s">
+      <c r="A41" s="130" t="s">
         <v>131</v>
       </c>
-      <c r="B41" s="172" t="s">
+      <c r="B41" s="135" t="s">
         <v>107</v>
       </c>
-      <c r="D41" s="175" t="s">
+      <c r="D41" s="138" t="s">
         <v>140</v>
       </c>
       <c r="E41" s="81">
@@ -7931,142 +7933,142 @@
       </c>
     </row>
     <row r="42" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A42" s="168" t="s">
+      <c r="A42" s="131" t="s">
         <v>131</v>
       </c>
-      <c r="B42" s="173" t="s">
+      <c r="B42" s="136" t="s">
         <v>106</v>
       </c>
-      <c r="D42" s="176" t="s">
+      <c r="D42" s="139" t="s">
         <v>139</v>
       </c>
       <c r="E42" s="87">
-        <f t="shared" ref="E42:E44" si="29">E22*F$35+E$35*F22-F22*F$35</f>
+        <f t="shared" ref="E42:E44" si="32">E22*F$35+E$35*F22-F22*F$35</f>
         <v>0.44000000000000017</v>
       </c>
-      <c r="F42" s="131">
-        <f t="shared" ref="F42:G42" si="30">F22*F$35</f>
+      <c r="F42">
+        <f t="shared" ref="F42:G42" si="33">F22*F$35</f>
         <v>1.5400000000000003</v>
       </c>
-      <c r="G42" s="131">
-        <f t="shared" si="30"/>
-        <v>3.52</v>
-      </c>
-      <c r="H42" s="88">
-        <f t="shared" ref="H42:H44" si="31">G22*H$35+G$35*H22-G22*G$35</f>
-        <v>5.0600000000000005</v>
-      </c>
-      <c r="I42" s="87">
-        <f t="shared" ref="I42:I44" si="32">I22*J$35+I$35*J22-J22*J$35</f>
-        <v>0.76</v>
-      </c>
-      <c r="J42" s="131">
-        <f t="shared" ref="J42:K42" si="33">J22*J$35</f>
-        <v>1.5400000000000003</v>
-      </c>
-      <c r="K42" s="131">
+      <c r="G42">
         <f t="shared" si="33"/>
         <v>3.52</v>
       </c>
+      <c r="H42" s="88">
+        <f t="shared" ref="H42:H44" si="34">G22*H$35+G$35*H22-G22*G$35</f>
+        <v>5.0600000000000005</v>
+      </c>
+      <c r="I42" s="87">
+        <f t="shared" ref="I42:I44" si="35">I22*J$35+I$35*J22-J22*J$35</f>
+        <v>0.76</v>
+      </c>
+      <c r="J42">
+        <f t="shared" ref="J42:K42" si="36">J22*J$35</f>
+        <v>1.5400000000000003</v>
+      </c>
+      <c r="K42">
+        <f t="shared" si="36"/>
+        <v>3.52</v>
+      </c>
       <c r="L42" s="88">
-        <f t="shared" ref="L42:L44" si="34">K22*L$35+K$35*L22-K22*K$35</f>
+        <f t="shared" ref="L42:L44" si="37">K22*L$35+K$35*L22-K22*K$35</f>
         <v>4.6000000000000014</v>
       </c>
     </row>
     <row r="43" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A43" s="168" t="s">
+      <c r="A43" s="131" t="s">
         <v>131</v>
       </c>
-      <c r="B43" s="173" t="s">
+      <c r="B43" s="136" t="s">
         <v>105</v>
       </c>
-      <c r="D43" s="176" t="s">
+      <c r="D43" s="139" t="s">
         <v>138</v>
       </c>
       <c r="E43" s="87">
-        <f t="shared" si="29"/>
+        <f t="shared" si="32"/>
         <v>2.2549999999999999</v>
       </c>
-      <c r="F43" s="131">
-        <f t="shared" ref="F43:G43" si="35">F23*F$35</f>
+      <c r="F43">
+        <f t="shared" ref="F43:G43" si="38">F23*F$35</f>
         <v>3.8500000000000005</v>
       </c>
-      <c r="G43" s="131">
+      <c r="G43">
+        <f t="shared" si="38"/>
+        <v>6.16</v>
+      </c>
+      <c r="H43" s="88">
+        <f t="shared" si="34"/>
+        <v>8.1950000000000003</v>
+      </c>
+      <c r="I43" s="87">
         <f t="shared" si="35"/>
+        <v>2.7399999999999993</v>
+      </c>
+      <c r="J43">
+        <f t="shared" ref="J43:K43" si="39">J23*J$35</f>
+        <v>3.8500000000000005</v>
+      </c>
+      <c r="K43">
+        <f t="shared" si="39"/>
         <v>6.16</v>
       </c>
-      <c r="H43" s="88">
-        <f t="shared" si="31"/>
-        <v>8.1950000000000003</v>
-      </c>
-      <c r="I43" s="87">
+      <c r="L43" s="88">
+        <f t="shared" si="37"/>
+        <v>7.57</v>
+      </c>
+    </row>
+    <row r="44" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A44" s="132" t="s">
+        <v>131</v>
+      </c>
+      <c r="B44" s="137" t="s">
+        <v>104</v>
+      </c>
+      <c r="D44" s="140" t="s">
+        <v>137</v>
+      </c>
+      <c r="E44" s="91">
         <f t="shared" si="32"/>
-        <v>2.7399999999999993</v>
-      </c>
-      <c r="J43" s="131">
-        <f t="shared" ref="J43:K43" si="36">J23*J$35</f>
-        <v>3.8500000000000005</v>
-      </c>
-      <c r="K43" s="131">
-        <f t="shared" si="36"/>
+        <v>4.84</v>
+      </c>
+      <c r="F44" s="93">
+        <f t="shared" ref="F44:G44" si="40">F24*F$35</f>
         <v>6.16</v>
       </c>
-      <c r="L43" s="88">
+      <c r="G44" s="93">
+        <f t="shared" si="40"/>
+        <v>8</v>
+      </c>
+      <c r="H44" s="94">
         <f t="shared" si="34"/>
-        <v>7.57</v>
-      </c>
-    </row>
-    <row r="44" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A44" s="169" t="s">
-        <v>131</v>
-      </c>
-      <c r="B44" s="174" t="s">
-        <v>104</v>
-      </c>
-      <c r="D44" s="177" t="s">
-        <v>137</v>
-      </c>
-      <c r="E44" s="91">
-        <f t="shared" si="29"/>
-        <v>4.84</v>
-      </c>
-      <c r="F44" s="93">
-        <f t="shared" ref="F44:G44" si="37">F24*F$35</f>
+        <v>9.5</v>
+      </c>
+      <c r="I44" s="91">
+        <f t="shared" si="35"/>
+        <v>4.7200000000000006</v>
+      </c>
+      <c r="J44" s="93">
+        <f t="shared" ref="J44:K44" si="41">J24*J$35</f>
         <v>6.16</v>
       </c>
-      <c r="G44" s="93">
+      <c r="K44" s="93">
+        <f t="shared" si="41"/>
+        <v>8</v>
+      </c>
+      <c r="L44" s="94">
         <f t="shared" si="37"/>
-        <v>8</v>
-      </c>
-      <c r="H44" s="94">
-        <f t="shared" si="31"/>
-        <v>9.5</v>
-      </c>
-      <c r="I44" s="91">
-        <f t="shared" si="32"/>
-        <v>4.7200000000000006</v>
-      </c>
-      <c r="J44" s="93">
-        <f t="shared" ref="J44:K44" si="38">J24*J$35</f>
-        <v>6.16</v>
-      </c>
-      <c r="K44" s="93">
-        <f t="shared" si="38"/>
-        <v>8</v>
-      </c>
-      <c r="L44" s="94">
-        <f t="shared" si="34"/>
         <v>9</v>
       </c>
     </row>
     <row r="45" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A45" s="167" t="s">
+      <c r="A45" s="130" t="s">
         <v>132</v>
       </c>
-      <c r="B45" s="172" t="s">
+      <c r="B45" s="135" t="s">
         <v>107</v>
       </c>
-      <c r="D45" s="175" t="s">
+      <c r="D45" s="138" t="s">
         <v>141</v>
       </c>
       <c r="E45" s="81">
@@ -8103,153 +8105,153 @@
       </c>
     </row>
     <row r="46" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A46" s="168" t="s">
+      <c r="A46" s="131" t="s">
         <v>132</v>
       </c>
-      <c r="B46" s="173" t="s">
+      <c r="B46" s="136" t="s">
         <v>106</v>
       </c>
-      <c r="D46" s="176" t="s">
+      <c r="D46" s="139" t="s">
         <v>146</v>
       </c>
       <c r="E46" s="87">
         <f>E22*F$36+E$36*F22-F22*F$36</f>
         <v>-0.10999999999999999</v>
       </c>
-      <c r="F46" s="131">
-        <f t="shared" ref="F46:G46" si="39">F22*F$36</f>
+      <c r="F46">
+        <f t="shared" ref="F46:G46" si="42">F22*F$36</f>
         <v>0.44000000000000006</v>
       </c>
-      <c r="G46" s="131">
-        <f t="shared" si="39"/>
-        <v>1.32</v>
-      </c>
-      <c r="H46" s="88">
-        <f t="shared" ref="H46:H48" si="40">G22*H$36+G$36*H22-G22*G$36</f>
-        <v>2.3099999999999996</v>
-      </c>
-      <c r="I46" s="87">
-        <f t="shared" ref="I46:I48" si="41">I22*J$36+I$36*J22-J22*J$36</f>
-        <v>5.9999999999999942E-2</v>
-      </c>
-      <c r="J46" s="131">
-        <f t="shared" ref="J46:K46" si="42">J22*J$36</f>
-        <v>0.44000000000000006</v>
-      </c>
-      <c r="K46" s="131">
+      <c r="G46">
         <f t="shared" si="42"/>
         <v>1.32</v>
       </c>
+      <c r="H46" s="88">
+        <f t="shared" ref="H46:H48" si="43">G22*H$36+G$36*H22-G22*G$36</f>
+        <v>2.3099999999999996</v>
+      </c>
+      <c r="I46" s="87">
+        <f t="shared" ref="I46:I48" si="44">I22*J$36+I$36*J22-J22*J$36</f>
+        <v>5.9999999999999942E-2</v>
+      </c>
+      <c r="J46">
+        <f t="shared" ref="J46:K46" si="45">J22*J$36</f>
+        <v>0.44000000000000006</v>
+      </c>
+      <c r="K46">
+        <f t="shared" si="45"/>
+        <v>1.32</v>
+      </c>
       <c r="L46" s="88">
-        <f t="shared" ref="L46:L48" si="43">K22*L$36+K$36*L22-K22*K$36</f>
+        <f t="shared" ref="L46:L48" si="46">K22*L$36+K$36*L22-K22*K$36</f>
         <v>2</v>
       </c>
     </row>
     <row r="47" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A47" s="168" t="s">
+      <c r="A47" s="131" t="s">
         <v>132</v>
       </c>
-      <c r="B47" s="173" t="s">
+      <c r="B47" s="136" t="s">
         <v>105</v>
       </c>
-      <c r="D47" s="176" t="s">
+      <c r="D47" s="139" t="s">
         <v>147</v>
       </c>
       <c r="E47" s="87">
-        <f t="shared" ref="E46:E48" si="44">E23*F$36+E$36*F23-F23*F$36</f>
+        <f t="shared" ref="E47:E48" si="47">E23*F$36+E$36*F23-F23*F$36</f>
         <v>5.500000000000016E-2</v>
       </c>
-      <c r="F47" s="131">
-        <f t="shared" ref="F47:G47" si="45">F23*F$36</f>
+      <c r="F47">
+        <f t="shared" ref="F47:G47" si="48">F23*F$36</f>
         <v>1.1000000000000001</v>
       </c>
-      <c r="G47" s="131">
-        <f t="shared" si="45"/>
+      <c r="G47">
+        <f t="shared" si="48"/>
         <v>2.31</v>
       </c>
       <c r="H47" s="88">
-        <f t="shared" si="40"/>
+        <f t="shared" si="43"/>
         <v>3.7950000000000004</v>
       </c>
       <c r="I47" s="87">
-        <f t="shared" si="41"/>
+        <f t="shared" si="44"/>
         <v>0.39000000000000012</v>
       </c>
-      <c r="J47" s="131">
-        <f t="shared" ref="J47:K47" si="46">J23*J$36</f>
+      <c r="J47">
+        <f t="shared" ref="J47:K47" si="49">J23*J$36</f>
         <v>1.1000000000000001</v>
       </c>
-      <c r="K47" s="131">
+      <c r="K47">
+        <f t="shared" si="49"/>
+        <v>2.31</v>
+      </c>
+      <c r="L47" s="88">
         <f t="shared" si="46"/>
-        <v>2.31</v>
-      </c>
-      <c r="L47" s="88">
+        <v>3.32</v>
+      </c>
+    </row>
+    <row r="48" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A48" s="132" t="s">
+        <v>132</v>
+      </c>
+      <c r="B48" s="137" t="s">
+        <v>104</v>
+      </c>
+      <c r="D48" s="140" t="s">
+        <v>148</v>
+      </c>
+      <c r="E48" s="91">
+        <f t="shared" si="47"/>
+        <v>0.44000000000000017</v>
+      </c>
+      <c r="F48" s="93">
+        <f t="shared" ref="F48:G48" si="50">F24*F$36</f>
+        <v>1.76</v>
+      </c>
+      <c r="G48" s="93">
+        <f t="shared" si="50"/>
+        <v>3</v>
+      </c>
+      <c r="H48" s="94">
         <f t="shared" si="43"/>
-        <v>3.32</v>
-      </c>
-    </row>
-    <row r="48" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A48" s="169" t="s">
-        <v>132</v>
-      </c>
-      <c r="B48" s="174" t="s">
-        <v>104</v>
-      </c>
-      <c r="D48" s="177" t="s">
-        <v>148</v>
-      </c>
-      <c r="E48" s="91">
+        <v>4.5</v>
+      </c>
+      <c r="I48" s="91">
         <f t="shared" si="44"/>
-        <v>0.44000000000000017</v>
-      </c>
-      <c r="F48" s="93">
-        <f t="shared" ref="F48:G48" si="47">F24*F$36</f>
+        <v>0.72</v>
+      </c>
+      <c r="J48" s="93">
+        <f t="shared" ref="J48:K48" si="51">J24*J$36</f>
         <v>1.76</v>
       </c>
-      <c r="G48" s="93">
-        <f t="shared" si="47"/>
+      <c r="K48" s="93">
+        <f t="shared" si="51"/>
         <v>3</v>
       </c>
-      <c r="H48" s="94">
-        <f t="shared" si="40"/>
-        <v>4.5</v>
-      </c>
-      <c r="I48" s="91">
-        <f t="shared" si="41"/>
-        <v>0.72</v>
-      </c>
-      <c r="J48" s="93">
-        <f t="shared" ref="J48:K48" si="48">J24*J$36</f>
-        <v>1.76</v>
-      </c>
-      <c r="K48" s="93">
-        <f t="shared" si="48"/>
-        <v>3</v>
-      </c>
       <c r="L48" s="94">
-        <f t="shared" si="43"/>
+        <f t="shared" si="46"/>
         <v>4</v>
       </c>
     </row>
     <row r="49" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A49" s="167" t="s">
+      <c r="A49" s="130" t="s">
         <v>133</v>
       </c>
-      <c r="B49" s="172" t="s">
+      <c r="B49" s="135" t="s">
         <v>107</v>
       </c>
-      <c r="D49" s="175" t="s">
+      <c r="D49" s="138" t="s">
         <v>143</v>
       </c>
       <c r="E49" s="87">
         <f>E21*F$37+E$37*F21-F21*F$37</f>
         <v>0</v>
       </c>
-      <c r="F49" s="131">
+      <c r="F49">
         <f>F21*F$37</f>
         <v>0</v>
       </c>
-      <c r="G49" s="131">
+      <c r="G49">
         <f>G21*G$37</f>
         <v>0.60499999999999998</v>
       </c>
@@ -8261,11 +8263,11 @@
         <f>I21*J$37+I$37*J21-J21*J$37</f>
         <v>0</v>
       </c>
-      <c r="J49" s="131">
+      <c r="J49">
         <f>J21*J$37</f>
         <v>0</v>
       </c>
-      <c r="K49" s="131">
+      <c r="K49">
         <f>K21*K$37</f>
         <v>0.60499999999999998</v>
       </c>
@@ -8275,136 +8277,163 @@
       </c>
     </row>
     <row r="50" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A50" s="168" t="s">
+      <c r="A50" s="131" t="s">
         <v>133</v>
       </c>
-      <c r="B50" s="173" t="s">
+      <c r="B50" s="136" t="s">
         <v>106</v>
       </c>
-      <c r="D50" s="176" t="s">
+      <c r="D50" s="139" t="s">
         <v>142</v>
       </c>
       <c r="E50" s="87">
-        <f t="shared" ref="E50:E52" si="49">E22*F$37+E$37*F22-F22*F$37</f>
+        <f t="shared" ref="E50:E52" si="52">E22*F$37+E$37*F22-F22*F$37</f>
         <v>0.16500000000000015</v>
       </c>
-      <c r="F50" s="131">
-        <f t="shared" ref="F50:G50" si="50">F22*F$37</f>
+      <c r="F50">
+        <f t="shared" ref="F50:G50" si="53">F22*F$37</f>
         <v>0.9900000000000001</v>
       </c>
-      <c r="G50" s="131">
-        <f t="shared" si="50"/>
-        <v>2.42</v>
-      </c>
-      <c r="H50" s="88">
-        <f t="shared" ref="H50:H52" si="51">G22*H$37+G$37*H22-G22*G$37</f>
-        <v>3.6850000000000005</v>
-      </c>
-      <c r="I50" s="87">
-        <f t="shared" ref="I50:I52" si="52">I22*J$37+I$37*J22-J22*J$37</f>
-        <v>0.41000000000000025</v>
-      </c>
-      <c r="J50" s="131">
-        <f t="shared" ref="J50:K50" si="53">J22*J$37</f>
-        <v>0.9900000000000001</v>
-      </c>
-      <c r="K50" s="131">
+      <c r="G50">
         <f t="shared" si="53"/>
         <v>2.42</v>
       </c>
+      <c r="H50" s="88">
+        <f t="shared" ref="H50:H52" si="54">G22*H$37+G$37*H22-G22*G$37</f>
+        <v>3.6850000000000005</v>
+      </c>
+      <c r="I50" s="87">
+        <f t="shared" ref="I50:I52" si="55">I22*J$37+I$37*J22-J22*J$37</f>
+        <v>0.41000000000000025</v>
+      </c>
+      <c r="J50">
+        <f t="shared" ref="J50:K50" si="56">J22*J$37</f>
+        <v>0.9900000000000001</v>
+      </c>
+      <c r="K50">
+        <f t="shared" si="56"/>
+        <v>2.42</v>
+      </c>
       <c r="L50" s="88">
-        <f t="shared" ref="L50:L52" si="54">K22*L$37+K$37*L22-K22*K$37</f>
+        <f t="shared" ref="L50:L52" si="57">K22*L$37+K$37*L22-K22*K$37</f>
         <v>3.3000000000000007</v>
       </c>
     </row>
     <row r="51" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A51" s="168" t="s">
+      <c r="A51" s="131" t="s">
         <v>133</v>
       </c>
-      <c r="B51" s="173" t="s">
+      <c r="B51" s="136" t="s">
         <v>105</v>
       </c>
-      <c r="D51" s="176" t="s">
+      <c r="D51" s="139" t="s">
         <v>144</v>
       </c>
       <c r="E51" s="87">
-        <f t="shared" si="49"/>
+        <f t="shared" si="52"/>
         <v>1.1550000000000002</v>
       </c>
-      <c r="F51" s="131">
-        <f t="shared" ref="F51:G51" si="55">F23*F$37</f>
+      <c r="F51">
+        <f t="shared" ref="F51:G51" si="58">F23*F$37</f>
         <v>2.4750000000000001</v>
       </c>
-      <c r="G51" s="131">
+      <c r="G51">
+        <f t="shared" si="58"/>
+        <v>4.2350000000000003</v>
+      </c>
+      <c r="H51" s="88">
+        <f t="shared" si="54"/>
+        <v>5.9950000000000001</v>
+      </c>
+      <c r="I51" s="87">
         <f t="shared" si="55"/>
+        <v>1.5650000000000008</v>
+      </c>
+      <c r="J51">
+        <f t="shared" ref="J51:K51" si="59">J23*J$37</f>
+        <v>2.4750000000000001</v>
+      </c>
+      <c r="K51">
+        <f t="shared" si="59"/>
         <v>4.2350000000000003</v>
       </c>
-      <c r="H51" s="88">
-        <f t="shared" si="51"/>
-        <v>5.9950000000000001</v>
-      </c>
-      <c r="I51" s="87">
+      <c r="L51" s="88">
+        <f t="shared" si="57"/>
+        <v>5.4449999999999994</v>
+      </c>
+    </row>
+    <row r="52" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A52" s="132" t="s">
+        <v>133</v>
+      </c>
+      <c r="B52" s="137" t="s">
+        <v>104</v>
+      </c>
+      <c r="D52" s="140" t="s">
+        <v>145</v>
+      </c>
+      <c r="E52" s="91">
         <f t="shared" si="52"/>
-        <v>1.5650000000000008</v>
-      </c>
-      <c r="J51" s="131">
-        <f t="shared" ref="J51:K51" si="56">J23*J$37</f>
-        <v>2.4750000000000001</v>
-      </c>
-      <c r="K51" s="131">
-        <f t="shared" si="56"/>
-        <v>4.2350000000000003</v>
-      </c>
-      <c r="L51" s="88">
+        <v>2.6399999999999997</v>
+      </c>
+      <c r="F52" s="93">
+        <f t="shared" ref="F52:G52" si="60">F24*F$37</f>
+        <v>3.96</v>
+      </c>
+      <c r="G52" s="93">
+        <f t="shared" si="60"/>
+        <v>5.5</v>
+      </c>
+      <c r="H52" s="94">
         <f t="shared" si="54"/>
-        <v>5.4449999999999994</v>
-      </c>
-    </row>
-    <row r="52" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A52" s="169" t="s">
-        <v>133</v>
-      </c>
-      <c r="B52" s="174" t="s">
-        <v>104</v>
-      </c>
-      <c r="D52" s="177" t="s">
-        <v>145</v>
-      </c>
-      <c r="E52" s="91">
-        <f t="shared" si="49"/>
-        <v>2.6399999999999997</v>
-      </c>
-      <c r="F52" s="93">
-        <f t="shared" ref="F52:G52" si="57">F24*F$37</f>
+        <v>7</v>
+      </c>
+      <c r="I52" s="91">
+        <f t="shared" si="55"/>
+        <v>2.7199999999999998</v>
+      </c>
+      <c r="J52" s="93">
+        <f t="shared" ref="J52:K52" si="61">J24*J$37</f>
         <v>3.96</v>
       </c>
-      <c r="G52" s="93">
+      <c r="K52" s="93">
+        <f t="shared" si="61"/>
+        <v>5.5</v>
+      </c>
+      <c r="L52" s="94">
         <f t="shared" si="57"/>
-        <v>5.5</v>
-      </c>
-      <c r="H52" s="94">
-        <f t="shared" si="51"/>
-        <v>7</v>
-      </c>
-      <c r="I52" s="91">
-        <f t="shared" si="52"/>
-        <v>2.7199999999999998</v>
-      </c>
-      <c r="J52" s="93">
-        <f t="shared" ref="J52:K52" si="58">J24*J$37</f>
-        <v>3.96</v>
-      </c>
-      <c r="K52" s="93">
-        <f t="shared" si="58"/>
-        <v>5.5</v>
-      </c>
-      <c r="L52" s="94">
-        <f t="shared" si="54"/>
         <v>6.5</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="35">
+    <mergeCell ref="A3:E3"/>
+    <mergeCell ref="A6:A7"/>
+    <mergeCell ref="B6:B7"/>
+    <mergeCell ref="C6:C7"/>
+    <mergeCell ref="D6:F6"/>
+    <mergeCell ref="AA6:AH6"/>
+    <mergeCell ref="AA7:AD7"/>
+    <mergeCell ref="AE7:AH7"/>
+    <mergeCell ref="E40:L40"/>
+    <mergeCell ref="AI6:AP6"/>
+    <mergeCell ref="J6:J7"/>
+    <mergeCell ref="E34:L34"/>
+    <mergeCell ref="K6:R6"/>
+    <mergeCell ref="O7:R7"/>
+    <mergeCell ref="K7:N7"/>
+    <mergeCell ref="S6:Z6"/>
+    <mergeCell ref="S7:V7"/>
+    <mergeCell ref="W7:Z7"/>
+    <mergeCell ref="G6:I6"/>
+    <mergeCell ref="AY6:BF6"/>
+    <mergeCell ref="AI7:AL7"/>
+    <mergeCell ref="AM7:AP7"/>
+    <mergeCell ref="AQ7:AT7"/>
+    <mergeCell ref="AU7:AX7"/>
+    <mergeCell ref="AY7:BB7"/>
+    <mergeCell ref="BC7:BF7"/>
+    <mergeCell ref="AQ6:AX6"/>
     <mergeCell ref="BS6:BT6"/>
     <mergeCell ref="BU6:BU7"/>
     <mergeCell ref="BG6:BN6"/>
@@ -8413,33 +8442,6 @@
     <mergeCell ref="BO6:BR6"/>
     <mergeCell ref="BO7:BP7"/>
     <mergeCell ref="BQ7:BR7"/>
-    <mergeCell ref="AY6:BF6"/>
-    <mergeCell ref="AI7:AL7"/>
-    <mergeCell ref="AM7:AP7"/>
-    <mergeCell ref="AQ7:AT7"/>
-    <mergeCell ref="AU7:AX7"/>
-    <mergeCell ref="AY7:BB7"/>
-    <mergeCell ref="BC7:BF7"/>
-    <mergeCell ref="AA6:AH6"/>
-    <mergeCell ref="AA7:AD7"/>
-    <mergeCell ref="AE7:AH7"/>
-    <mergeCell ref="E40:L40"/>
-    <mergeCell ref="AI6:AP6"/>
-    <mergeCell ref="AQ6:AX6"/>
-    <mergeCell ref="J6:J7"/>
-    <mergeCell ref="E34:L34"/>
-    <mergeCell ref="K6:R6"/>
-    <mergeCell ref="O7:R7"/>
-    <mergeCell ref="K7:N7"/>
-    <mergeCell ref="S6:Z6"/>
-    <mergeCell ref="S7:V7"/>
-    <mergeCell ref="W7:Z7"/>
-    <mergeCell ref="A3:E3"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="B6:B7"/>
-    <mergeCell ref="C6:C7"/>
-    <mergeCell ref="D6:F6"/>
-    <mergeCell ref="G6:I6"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="B2" r:id="rId1" xr:uid="{4DC97A13-A5A9-447D-88B6-BFF061BE3C83}"/>
@@ -8486,17 +8488,17 @@
     </row>
     <row r="4" spans="2:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="5" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B5" s="112" t="s">
+      <c r="B5" s="158" t="s">
         <v>7</v>
       </c>
-      <c r="C5" s="109" t="s">
+      <c r="C5" s="155" t="s">
         <v>6</v>
       </c>
-      <c r="D5" s="110"/>
-      <c r="E5" s="111"/>
+      <c r="D5" s="156"/>
+      <c r="E5" s="157"/>
     </row>
     <row r="6" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B6" s="113"/>
+      <c r="B6" s="159"/>
       <c r="C6" s="30" t="s">
         <v>8</v>
       </c>
@@ -8627,18 +8629,18 @@
       <c r="B15" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="C15" s="114" t="s">
+      <c r="C15" s="160" t="s">
         <v>17</v>
       </c>
-      <c r="D15" s="115"/>
-      <c r="E15" s="115"/>
-      <c r="F15" s="116"/>
-      <c r="G15" s="114" t="s">
+      <c r="D15" s="161"/>
+      <c r="E15" s="161"/>
+      <c r="F15" s="162"/>
+      <c r="G15" s="160" t="s">
         <v>18</v>
       </c>
-      <c r="H15" s="115"/>
-      <c r="I15" s="115"/>
-      <c r="J15" s="116"/>
+      <c r="H15" s="161"/>
+      <c r="I15" s="161"/>
+      <c r="J15" s="162"/>
     </row>
     <row r="16" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B16" s="15" t="s">
@@ -9070,18 +9072,18 @@
       <c r="B33" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="C33" s="119" t="s">
+      <c r="C33" s="188" t="s">
         <v>17</v>
       </c>
-      <c r="D33" s="120"/>
-      <c r="E33" s="120"/>
-      <c r="F33" s="121"/>
-      <c r="G33" s="114" t="s">
+      <c r="D33" s="189"/>
+      <c r="E33" s="189"/>
+      <c r="F33" s="190"/>
+      <c r="G33" s="160" t="s">
         <v>18</v>
       </c>
-      <c r="H33" s="115"/>
-      <c r="I33" s="115"/>
-      <c r="J33" s="116"/>
+      <c r="H33" s="161"/>
+      <c r="I33" s="161"/>
+      <c r="J33" s="162"/>
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B34" s="15" t="s">
@@ -9491,18 +9493,18 @@
       <c r="B51" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="C51" s="114" t="s">
+      <c r="C51" s="160" t="s">
         <v>17</v>
       </c>
-      <c r="D51" s="115"/>
-      <c r="E51" s="115"/>
-      <c r="F51" s="116"/>
-      <c r="G51" s="114" t="s">
+      <c r="D51" s="161"/>
+      <c r="E51" s="161"/>
+      <c r="F51" s="162"/>
+      <c r="G51" s="160" t="s">
         <v>18</v>
       </c>
-      <c r="H51" s="115"/>
-      <c r="I51" s="115"/>
-      <c r="J51" s="116"/>
+      <c r="H51" s="161"/>
+      <c r="I51" s="161"/>
+      <c r="J51" s="162"/>
     </row>
     <row r="52" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B52" s="15" t="s">
@@ -9932,17 +9934,17 @@
     </row>
     <row r="4" spans="2:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="5" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B5" s="112" t="s">
+      <c r="B5" s="158" t="s">
         <v>7</v>
       </c>
-      <c r="C5" s="109" t="s">
+      <c r="C5" s="155" t="s">
         <v>6</v>
       </c>
-      <c r="D5" s="110"/>
-      <c r="E5" s="111"/>
+      <c r="D5" s="156"/>
+      <c r="E5" s="157"/>
     </row>
     <row r="6" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B6" s="113"/>
+      <c r="B6" s="159"/>
       <c r="C6" s="30" t="s">
         <v>8</v>
       </c>
@@ -10073,18 +10075,18 @@
       <c r="B15" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="C15" s="114" t="s">
+      <c r="C15" s="160" t="s">
         <v>17</v>
       </c>
-      <c r="D15" s="115"/>
-      <c r="E15" s="115"/>
-      <c r="F15" s="116"/>
-      <c r="G15" s="114" t="s">
+      <c r="D15" s="161"/>
+      <c r="E15" s="161"/>
+      <c r="F15" s="162"/>
+      <c r="G15" s="160" t="s">
         <v>18</v>
       </c>
-      <c r="H15" s="115"/>
-      <c r="I15" s="115"/>
-      <c r="J15" s="116"/>
+      <c r="H15" s="161"/>
+      <c r="I15" s="161"/>
+      <c r="J15" s="162"/>
     </row>
     <row r="16" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B16" s="15" t="s">
@@ -10484,18 +10486,18 @@
       <c r="B33" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="C33" s="114" t="s">
+      <c r="C33" s="160" t="s">
         <v>17</v>
       </c>
-      <c r="D33" s="115"/>
-      <c r="E33" s="115"/>
-      <c r="F33" s="116"/>
-      <c r="G33" s="114" t="s">
+      <c r="D33" s="161"/>
+      <c r="E33" s="161"/>
+      <c r="F33" s="162"/>
+      <c r="G33" s="160" t="s">
         <v>18</v>
       </c>
-      <c r="H33" s="115"/>
-      <c r="I33" s="115"/>
-      <c r="J33" s="116"/>
+      <c r="H33" s="161"/>
+      <c r="I33" s="161"/>
+      <c r="J33" s="162"/>
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B34" s="15" t="s">
@@ -10873,18 +10875,18 @@
       <c r="B51" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="C51" s="114" t="s">
+      <c r="C51" s="160" t="s">
         <v>17</v>
       </c>
-      <c r="D51" s="115"/>
-      <c r="E51" s="115"/>
-      <c r="F51" s="116"/>
-      <c r="G51" s="114" t="s">
+      <c r="D51" s="161"/>
+      <c r="E51" s="161"/>
+      <c r="F51" s="162"/>
+      <c r="G51" s="160" t="s">
         <v>18</v>
       </c>
-      <c r="H51" s="115"/>
-      <c r="I51" s="115"/>
-      <c r="J51" s="116"/>
+      <c r="H51" s="161"/>
+      <c r="I51" s="161"/>
+      <c r="J51" s="162"/>
     </row>
     <row r="52" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B52" s="15" t="s">
@@ -11317,11 +11319,11 @@
         <f>E4-0.11</f>
         <v>0.11000000000000003</v>
       </c>
-      <c r="E4" s="133">
+      <c r="E4" s="111">
         <f>B4-0.11</f>
         <v>0.22000000000000003</v>
       </c>
-      <c r="F4" s="131">
+      <c r="F4">
         <f>B4+0.11</f>
         <v>0.44</v>
       </c>
@@ -11333,11 +11335,11 @@
         <f>I4-0.08</f>
         <v>0.14000000000000001</v>
       </c>
-      <c r="I4" s="131">
+      <c r="I4">
         <f t="shared" ref="I4:I6" si="1">E4</f>
         <v>0.22000000000000003</v>
       </c>
-      <c r="J4" s="131">
+      <c r="J4">
         <f t="shared" ref="J4:J6" si="2">F4</f>
         <v>0.44</v>
       </c>
@@ -11357,11 +11359,11 @@
         <f t="shared" ref="D5" si="4">E5-0.11</f>
         <v>0.44000000000000006</v>
       </c>
-      <c r="E5" s="133">
+      <c r="E5" s="111">
         <f t="shared" ref="E5" si="5">B5-0.11</f>
         <v>0.55000000000000004</v>
       </c>
-      <c r="F5" s="131">
+      <c r="F5">
         <f t="shared" ref="F5" si="6">B5+0.11</f>
         <v>0.77</v>
       </c>
@@ -11373,11 +11375,11 @@
         <f t="shared" ref="H5:H6" si="7">I5-0.08</f>
         <v>0.47000000000000003</v>
       </c>
-      <c r="I5" s="131">
+      <c r="I5">
         <f t="shared" si="1"/>
         <v>0.55000000000000004</v>
       </c>
-      <c r="J5" s="131">
+      <c r="J5">
         <f t="shared" si="2"/>
         <v>0.77</v>
       </c>
@@ -11479,11 +11481,11 @@
         <f>E10-1.5</f>
         <v>0.5</v>
       </c>
-      <c r="E10" s="133">
+      <c r="E10" s="111">
         <f>B10-0.5</f>
         <v>2</v>
       </c>
-      <c r="F10" s="131">
+      <c r="F10">
         <f>B10+0.5</f>
         <v>3</v>
       </c>
@@ -11495,11 +11497,11 @@
         <f>I10-1</f>
         <v>1</v>
       </c>
-      <c r="I10" s="131">
+      <c r="I10">
         <f t="shared" ref="I10:I12" si="9">E10</f>
         <v>2</v>
       </c>
-      <c r="J10" s="131">
+      <c r="J10">
         <f t="shared" ref="J10:J12" si="10">F10</f>
         <v>3</v>
       </c>
@@ -11519,11 +11521,11 @@
         <f t="shared" ref="D11:D12" si="12">E11-1.5</f>
         <v>3</v>
       </c>
-      <c r="E11" s="133">
+      <c r="E11" s="111">
         <f t="shared" ref="E11:E12" si="13">B11-0.5</f>
         <v>4.5</v>
       </c>
-      <c r="F11" s="131">
+      <c r="F11">
         <f t="shared" ref="F11:F12" si="14">B11+0.5</f>
         <v>5.5</v>
       </c>
@@ -11535,11 +11537,11 @@
         <f t="shared" ref="H11:H12" si="15">I11-1</f>
         <v>3.5</v>
       </c>
-      <c r="I11" s="131">
+      <c r="I11">
         <f t="shared" si="9"/>
         <v>4.5</v>
       </c>
-      <c r="J11" s="131">
+      <c r="J11">
         <f t="shared" si="10"/>
         <v>5.5</v>
       </c>
@@ -11678,11 +11680,11 @@
         <f>E5-0.4</f>
         <v>0.29999999999999993</v>
       </c>
-      <c r="E5" s="133">
+      <c r="E5" s="111">
         <f>B5-0.3</f>
         <v>0.7</v>
       </c>
-      <c r="F5" s="131">
+      <c r="F5">
         <f>B5+0.3</f>
         <v>1.3</v>
       </c>
@@ -11721,11 +11723,11 @@
         <f t="shared" ref="D6:D9" si="4">E6-0.4</f>
         <v>1.2999999999999998</v>
       </c>
-      <c r="E6" s="133">
+      <c r="E6" s="111">
         <f t="shared" ref="E6:E9" si="5">B6-0.3</f>
         <v>1.7</v>
       </c>
-      <c r="F6" s="131">
+      <c r="F6">
         <f t="shared" ref="F6:F9" si="6">B6+0.3</f>
         <v>2.2999999999999998</v>
       </c>
@@ -11764,11 +11766,11 @@
         <f t="shared" si="4"/>
         <v>2.3000000000000003</v>
       </c>
-      <c r="E7" s="133">
+      <c r="E7" s="111">
         <f t="shared" si="5"/>
         <v>2.7</v>
       </c>
-      <c r="F7" s="131">
+      <c r="F7">
         <f t="shared" si="6"/>
         <v>3.3</v>
       </c>
@@ -11807,11 +11809,11 @@
         <f t="shared" si="4"/>
         <v>3.3000000000000003</v>
       </c>
-      <c r="E8" s="133">
+      <c r="E8" s="111">
         <f t="shared" si="5"/>
         <v>3.7</v>
       </c>
-      <c r="F8" s="131">
+      <c r="F8">
         <f t="shared" si="6"/>
         <v>4.3</v>
       </c>
@@ -11940,11 +11942,11 @@
         <f>E13-0.4</f>
         <v>0.29999999999999993</v>
       </c>
-      <c r="E13" s="133">
+      <c r="E13" s="111">
         <f>B13-0.3</f>
         <v>0.7</v>
       </c>
-      <c r="F13" s="131">
+      <c r="F13">
         <f>B13+0.3</f>
         <v>1.3</v>
       </c>
@@ -11983,11 +11985,11 @@
         <f t="shared" ref="D14:D17" si="12">E14-0.4</f>
         <v>1.2999999999999998</v>
       </c>
-      <c r="E14" s="133">
+      <c r="E14" s="111">
         <f t="shared" ref="E14:E17" si="13">B14-0.3</f>
         <v>1.7</v>
       </c>
-      <c r="F14" s="131">
+      <c r="F14">
         <f t="shared" ref="F14:F17" si="14">B14+0.3</f>
         <v>2.2999999999999998</v>
       </c>
@@ -12026,11 +12028,11 @@
         <f t="shared" si="12"/>
         <v>2.3000000000000003</v>
       </c>
-      <c r="E15" s="133">
+      <c r="E15" s="111">
         <f t="shared" si="13"/>
         <v>2.7</v>
       </c>
-      <c r="F15" s="131">
+      <c r="F15">
         <f t="shared" si="14"/>
         <v>3.3</v>
       </c>
@@ -12069,11 +12071,11 @@
         <f t="shared" si="12"/>
         <v>3.3000000000000003</v>
       </c>
-      <c r="E16" s="133">
+      <c r="E16" s="111">
         <f t="shared" si="13"/>
         <v>3.7</v>
       </c>
-      <c r="F16" s="131">
+      <c r="F16">
         <f t="shared" si="14"/>
         <v>4.3</v>
       </c>
@@ -12202,11 +12204,11 @@
         <f>E21-0.4</f>
         <v>0.29999999999999993</v>
       </c>
-      <c r="E21" s="133">
+      <c r="E21" s="111">
         <f>B21-0.3</f>
         <v>0.7</v>
       </c>
-      <c r="F21" s="131">
+      <c r="F21">
         <f>B21+0.3</f>
         <v>1.3</v>
       </c>
@@ -12245,11 +12247,11 @@
         <f t="shared" ref="D22:D25" si="20">E22-0.4</f>
         <v>1.2999999999999998</v>
       </c>
-      <c r="E22" s="133">
+      <c r="E22" s="111">
         <f t="shared" ref="E22:E25" si="21">B22-0.3</f>
         <v>1.7</v>
       </c>
-      <c r="F22" s="131">
+      <c r="F22">
         <f t="shared" ref="F22:F25" si="22">B22+0.3</f>
         <v>2.2999999999999998</v>
       </c>
@@ -12288,11 +12290,11 @@
         <f t="shared" si="20"/>
         <v>2.3000000000000003</v>
       </c>
-      <c r="E23" s="133">
+      <c r="E23" s="111">
         <f t="shared" si="21"/>
         <v>2.7</v>
       </c>
-      <c r="F23" s="131">
+      <c r="F23">
         <f t="shared" si="22"/>
         <v>3.3</v>
       </c>
@@ -12331,11 +12333,11 @@
         <f t="shared" si="20"/>
         <v>3.3000000000000003</v>
       </c>
-      <c r="E24" s="133">
+      <c r="E24" s="111">
         <f t="shared" si="21"/>
         <v>3.7</v>
       </c>
-      <c r="F24" s="131">
+      <c r="F24">
         <f t="shared" si="22"/>
         <v>4.3</v>
       </c>
@@ -12464,11 +12466,11 @@
         <f>E29-0.4</f>
         <v>0.29999999999999993</v>
       </c>
-      <c r="E29" s="133">
+      <c r="E29" s="111">
         <f>B29-0.3</f>
         <v>0.7</v>
       </c>
-      <c r="F29" s="131">
+      <c r="F29">
         <f>B29+0.3</f>
         <v>1.3</v>
       </c>
@@ -12507,11 +12509,11 @@
         <f t="shared" ref="D30:D33" si="28">E30-0.4</f>
         <v>1.2999999999999998</v>
       </c>
-      <c r="E30" s="133">
+      <c r="E30" s="111">
         <f t="shared" ref="E30:E33" si="29">B30-0.3</f>
         <v>1.7</v>
       </c>
-      <c r="F30" s="131">
+      <c r="F30">
         <f t="shared" ref="F30:F33" si="30">B30+0.3</f>
         <v>2.2999999999999998</v>
       </c>
@@ -12550,11 +12552,11 @@
         <f t="shared" si="28"/>
         <v>2.3000000000000003</v>
       </c>
-      <c r="E31" s="133">
+      <c r="E31" s="111">
         <f t="shared" si="29"/>
         <v>2.7</v>
       </c>
-      <c r="F31" s="131">
+      <c r="F31">
         <f t="shared" si="30"/>
         <v>3.3</v>
       </c>
@@ -12593,11 +12595,11 @@
         <f t="shared" si="28"/>
         <v>3.3000000000000003</v>
       </c>
-      <c r="E32" s="133">
+      <c r="E32" s="111">
         <f t="shared" si="29"/>
         <v>3.7</v>
       </c>
-      <c r="F32" s="131">
+      <c r="F32">
         <f t="shared" si="30"/>
         <v>4.3</v>
       </c>
@@ -12731,11 +12733,11 @@
         <f>E39-0.4</f>
         <v>0.29999999999999993</v>
       </c>
-      <c r="E39" s="133">
+      <c r="E39" s="111">
         <f>B39-0.3</f>
         <v>0.7</v>
       </c>
-      <c r="F39" s="131">
+      <c r="F39">
         <f>B39+0.3</f>
         <v>1.3</v>
       </c>
@@ -12774,11 +12776,11 @@
         <f t="shared" ref="D40:D43" si="36">E40-0.4</f>
         <v>1.2999999999999998</v>
       </c>
-      <c r="E40" s="133">
+      <c r="E40" s="111">
         <f t="shared" ref="E40:E43" si="37">B40-0.3</f>
         <v>1.7</v>
       </c>
-      <c r="F40" s="131">
+      <c r="F40">
         <f t="shared" ref="F40:F43" si="38">B40+0.3</f>
         <v>2.2999999999999998</v>
       </c>
@@ -12817,11 +12819,11 @@
         <f t="shared" si="36"/>
         <v>2.3000000000000003</v>
       </c>
-      <c r="E41" s="133">
+      <c r="E41" s="111">
         <f t="shared" si="37"/>
         <v>2.7</v>
       </c>
-      <c r="F41" s="131">
+      <c r="F41">
         <f t="shared" si="38"/>
         <v>3.3</v>
       </c>
@@ -12860,11 +12862,11 @@
         <f t="shared" si="36"/>
         <v>3.3000000000000003</v>
       </c>
-      <c r="E42" s="133">
+      <c r="E42" s="111">
         <f t="shared" si="37"/>
         <v>3.7</v>
       </c>
-      <c r="F42" s="131">
+      <c r="F42">
         <f t="shared" si="38"/>
         <v>4.3</v>
       </c>
@@ -12990,11 +12992,11 @@
         <f>E47-0.4</f>
         <v>0.29999999999999993</v>
       </c>
-      <c r="E47" s="133">
+      <c r="E47" s="111">
         <f>B47-0.3</f>
         <v>0.7</v>
       </c>
-      <c r="F47" s="131">
+      <c r="F47">
         <f>B47+0.3</f>
         <v>1.3</v>
       </c>
@@ -13033,11 +13035,11 @@
         <f t="shared" ref="D48:D51" si="44">E48-0.4</f>
         <v>1.2999999999999998</v>
       </c>
-      <c r="E48" s="133">
+      <c r="E48" s="111">
         <f t="shared" ref="E48:E51" si="45">B48-0.3</f>
         <v>1.7</v>
       </c>
-      <c r="F48" s="131">
+      <c r="F48">
         <f t="shared" ref="F48:F51" si="46">B48+0.3</f>
         <v>2.2999999999999998</v>
       </c>
@@ -13076,11 +13078,11 @@
         <f t="shared" si="44"/>
         <v>2.3000000000000003</v>
       </c>
-      <c r="E49" s="133">
+      <c r="E49" s="111">
         <f t="shared" si="45"/>
         <v>2.7</v>
       </c>
-      <c r="F49" s="131">
+      <c r="F49">
         <f t="shared" si="46"/>
         <v>3.3</v>
       </c>
@@ -13119,11 +13121,11 @@
         <f t="shared" si="44"/>
         <v>3.3000000000000003</v>
       </c>
-      <c r="E50" s="133">
+      <c r="E50" s="111">
         <f t="shared" si="45"/>
         <v>3.7</v>
       </c>
-      <c r="F50" s="131">
+      <c r="F50">
         <f t="shared" si="46"/>
         <v>4.3</v>
       </c>
@@ -13252,11 +13254,11 @@
         <f>E55-0.4</f>
         <v>0.29999999999999993</v>
       </c>
-      <c r="E55" s="133">
+      <c r="E55" s="111">
         <f>B55-0.3</f>
         <v>0.7</v>
       </c>
-      <c r="F55" s="131">
+      <c r="F55">
         <f>B55+0.3</f>
         <v>1.3</v>
       </c>
@@ -13295,11 +13297,11 @@
         <f t="shared" ref="D56:D59" si="52">E56-0.4</f>
         <v>1.2999999999999998</v>
       </c>
-      <c r="E56" s="133">
+      <c r="E56" s="111">
         <f t="shared" ref="E56:E59" si="53">B56-0.3</f>
         <v>1.7</v>
       </c>
-      <c r="F56" s="131">
+      <c r="F56">
         <f t="shared" ref="F56:F59" si="54">B56+0.3</f>
         <v>2.2999999999999998</v>
       </c>
@@ -13338,11 +13340,11 @@
         <f t="shared" si="52"/>
         <v>2.3000000000000003</v>
       </c>
-      <c r="E57" s="133">
+      <c r="E57" s="111">
         <f t="shared" si="53"/>
         <v>2.7</v>
       </c>
-      <c r="F57" s="131">
+      <c r="F57">
         <f t="shared" si="54"/>
         <v>3.3</v>
       </c>
@@ -13381,11 +13383,11 @@
         <f t="shared" si="52"/>
         <v>3.3000000000000003</v>
       </c>
-      <c r="E58" s="133">
+      <c r="E58" s="111">
         <f t="shared" si="53"/>
         <v>3.7</v>
       </c>
-      <c r="F58" s="131">
+      <c r="F58">
         <f t="shared" si="54"/>
         <v>4.3</v>
       </c>
@@ -13511,11 +13513,11 @@
         <f>E63-0.4</f>
         <v>0.29999999999999993</v>
       </c>
-      <c r="E63" s="133">
+      <c r="E63" s="111">
         <f>B63-0.3</f>
         <v>0.7</v>
       </c>
-      <c r="F63" s="131">
+      <c r="F63">
         <f>B63+0.3</f>
         <v>1.3</v>
       </c>
@@ -13554,11 +13556,11 @@
         <f t="shared" ref="D64:D67" si="60">E64-0.4</f>
         <v>1.2999999999999998</v>
       </c>
-      <c r="E64" s="133">
+      <c r="E64" s="111">
         <f t="shared" ref="E64:E67" si="61">B64-0.3</f>
         <v>1.7</v>
       </c>
-      <c r="F64" s="131">
+      <c r="F64">
         <f t="shared" ref="F64:F67" si="62">B64+0.3</f>
         <v>2.2999999999999998</v>
       </c>
@@ -13597,11 +13599,11 @@
         <f t="shared" si="60"/>
         <v>2.3000000000000003</v>
       </c>
-      <c r="E65" s="133">
+      <c r="E65" s="111">
         <f t="shared" si="61"/>
         <v>2.7</v>
       </c>
-      <c r="F65" s="131">
+      <c r="F65">
         <f t="shared" si="62"/>
         <v>3.3</v>
       </c>
@@ -13640,11 +13642,11 @@
         <f t="shared" si="60"/>
         <v>3.3000000000000003</v>
       </c>
-      <c r="E66" s="133">
+      <c r="E66" s="111">
         <f t="shared" si="61"/>
         <v>3.7</v>
       </c>
-      <c r="F66" s="131">
+      <c r="F66">
         <f t="shared" si="62"/>
         <v>4.3</v>
       </c>
@@ -13775,11 +13777,11 @@
         <f>E72-0.4</f>
         <v>0.29999999999999993</v>
       </c>
-      <c r="E72" s="133">
+      <c r="E72" s="111">
         <f>B72-0.3</f>
         <v>0.7</v>
       </c>
-      <c r="F72" s="131">
+      <c r="F72">
         <f>B72+0.3</f>
         <v>1.3</v>
       </c>
@@ -13818,11 +13820,11 @@
         <f t="shared" ref="D73:D76" si="68">E73-0.4</f>
         <v>1.2999999999999998</v>
       </c>
-      <c r="E73" s="133">
+      <c r="E73" s="111">
         <f t="shared" ref="E73:E76" si="69">B73-0.3</f>
         <v>1.7</v>
       </c>
-      <c r="F73" s="131">
+      <c r="F73">
         <f t="shared" ref="F73:F76" si="70">B73+0.3</f>
         <v>2.2999999999999998</v>
       </c>
@@ -13861,11 +13863,11 @@
         <f t="shared" si="68"/>
         <v>2.3000000000000003</v>
       </c>
-      <c r="E74" s="133">
+      <c r="E74" s="111">
         <f t="shared" si="69"/>
         <v>2.7</v>
       </c>
-      <c r="F74" s="131">
+      <c r="F74">
         <f t="shared" si="70"/>
         <v>3.3</v>
       </c>
@@ -13904,11 +13906,11 @@
         <f t="shared" si="68"/>
         <v>3.3000000000000003</v>
       </c>
-      <c r="E75" s="133">
+      <c r="E75" s="111">
         <f t="shared" si="69"/>
         <v>3.7</v>
       </c>
-      <c r="F75" s="131">
+      <c r="F75">
         <f t="shared" si="70"/>
         <v>4.3</v>
       </c>
@@ -14037,11 +14039,11 @@
         <f>E80-0.4</f>
         <v>0.29999999999999993</v>
       </c>
-      <c r="E80" s="133">
+      <c r="E80" s="111">
         <f>B80-0.3</f>
         <v>0.7</v>
       </c>
-      <c r="F80" s="131">
+      <c r="F80">
         <f>B80+0.3</f>
         <v>1.3</v>
       </c>
@@ -14080,11 +14082,11 @@
         <f t="shared" ref="D81:D84" si="76">E81-0.4</f>
         <v>1.2999999999999998</v>
       </c>
-      <c r="E81" s="133">
+      <c r="E81" s="111">
         <f t="shared" ref="E81:E84" si="77">B81-0.3</f>
         <v>1.7</v>
       </c>
-      <c r="F81" s="131">
+      <c r="F81">
         <f t="shared" ref="F81:F84" si="78">B81+0.3</f>
         <v>2.2999999999999998</v>
       </c>
@@ -14123,11 +14125,11 @@
         <f t="shared" si="76"/>
         <v>2.3000000000000003</v>
       </c>
-      <c r="E82" s="133">
+      <c r="E82" s="111">
         <f t="shared" si="77"/>
         <v>2.7</v>
       </c>
-      <c r="F82" s="131">
+      <c r="F82">
         <f t="shared" si="78"/>
         <v>3.3</v>
       </c>
@@ -14166,11 +14168,11 @@
         <f t="shared" si="76"/>
         <v>3.3000000000000003</v>
       </c>
-      <c r="E83" s="133">
+      <c r="E83" s="111">
         <f t="shared" si="77"/>
         <v>3.7</v>
       </c>
-      <c r="F83" s="131">
+      <c r="F83">
         <f t="shared" si="78"/>
         <v>4.3</v>
       </c>
@@ -14299,11 +14301,11 @@
         <f>E88-0.4</f>
         <v>0.29999999999999993</v>
       </c>
-      <c r="E88" s="133">
+      <c r="E88" s="111">
         <f>B88-0.3</f>
         <v>0.7</v>
       </c>
-      <c r="F88" s="131">
+      <c r="F88">
         <f>B88+0.3</f>
         <v>1.3</v>
       </c>
@@ -14342,11 +14344,11 @@
         <f t="shared" ref="D89:D92" si="84">E89-0.4</f>
         <v>1.2999999999999998</v>
       </c>
-      <c r="E89" s="133">
+      <c r="E89" s="111">
         <f t="shared" ref="E89:E92" si="85">B89-0.3</f>
         <v>1.7</v>
       </c>
-      <c r="F89" s="131">
+      <c r="F89">
         <f t="shared" ref="F89:F92" si="86">B89+0.3</f>
         <v>2.2999999999999998</v>
       </c>
@@ -14385,11 +14387,11 @@
         <f t="shared" si="84"/>
         <v>2.3000000000000003</v>
       </c>
-      <c r="E90" s="133">
+      <c r="E90" s="111">
         <f t="shared" si="85"/>
         <v>2.7</v>
       </c>
-      <c r="F90" s="131">
+      <c r="F90">
         <f t="shared" si="86"/>
         <v>3.3</v>
       </c>
@@ -14428,11 +14430,11 @@
         <f t="shared" si="84"/>
         <v>3.3000000000000003</v>
       </c>
-      <c r="E91" s="133">
+      <c r="E91" s="111">
         <f t="shared" si="85"/>
         <v>3.7</v>
       </c>
-      <c r="F91" s="131">
+      <c r="F91">
         <f t="shared" si="86"/>
         <v>4.3</v>
       </c>
